--- a/research/traditional_assets/database/data/egypt/egypt_household_products.xlsx
+++ b/research/traditional_assets/database/data/egypt/egypt_household_products.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="case_mcro" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -351,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +581,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,115 +590,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.1189</v>
+        <v>0.0251</v>
       </c>
       <c r="E2">
-        <v>0.401</v>
+        <v>0.155</v>
       </c>
       <c r="G2">
-        <v>-0.009520905923344947</v>
+        <v>0.0724616292798111</v>
       </c>
       <c r="H2">
-        <v>-0.009520905923344947</v>
+        <v>0.0724616292798111</v>
       </c>
       <c r="I2">
-        <v>-0.01778745644599303</v>
+        <v>0.06195985832349469</v>
       </c>
       <c r="J2">
-        <v>-0.01390184702817902</v>
+        <v>0.05377683012300412</v>
       </c>
       <c r="K2">
-        <v>-0.5640000000000001</v>
+        <v>5.75</v>
       </c>
       <c r="L2">
-        <v>-0.004912891986062718</v>
+        <v>0.03394332939787485</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.05330964015992892</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0.8347826086956521</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.0392047978676144</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0.6139130434782608</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.27</v>
+      </c>
+      <c r="T2">
+        <v>0.2645833333333333</v>
       </c>
       <c r="U2">
-        <v>2.88</v>
+        <v>4.901</v>
       </c>
       <c r="V2">
-        <v>0.1507853403141361</v>
+        <v>0.0544313638382941</v>
       </c>
       <c r="W2">
-        <v>0.001443179513919063</v>
+        <v>0.2011661807580175</v>
       </c>
       <c r="X2">
-        <v>0.1125780732786648</v>
+        <v>0.191980886416965</v>
       </c>
       <c r="Y2">
-        <v>-0.1111348937647458</v>
+        <v>0.009185294341052475</v>
       </c>
       <c r="Z2">
-        <v>9.931654987455662</v>
+        <v>5.567057740970784</v>
       </c>
       <c r="AA2">
-        <v>-0.267907661239789</v>
+        <v>0.1338149858483539</v>
       </c>
       <c r="AB2">
-        <v>0.1101906588437981</v>
+        <v>0.1878311663494354</v>
       </c>
       <c r="AC2">
-        <v>-0.3780983200835871</v>
+        <v>-0.05304832295133535</v>
       </c>
       <c r="AD2">
-        <v>0.764</v>
+        <v>7.205</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.764</v>
+        <v>7.205</v>
       </c>
       <c r="AG2">
-        <v>-2.116</v>
+        <v>2.304</v>
       </c>
       <c r="AH2">
-        <v>0.03846153846153846</v>
+        <v>0.07409121291583115</v>
       </c>
       <c r="AI2">
-        <v>0.05657582938388626</v>
+        <v>0.2172536485345555</v>
       </c>
       <c r="AJ2">
-        <v>-0.1245878473857748</v>
+        <v>0.02495018626007104</v>
       </c>
       <c r="AK2">
-        <v>-0.1991716867469879</v>
+        <v>0.08152000849166757</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>0.61</v>
       </c>
       <c r="AM2">
-        <v>-0.109</v>
+        <v>0.244</v>
       </c>
       <c r="AN2">
-        <v>-1.197492163009404</v>
+        <v>0.6234856351678781</v>
+      </c>
+      <c r="AO2">
+        <v>17.20655737704918</v>
       </c>
       <c r="AP2">
-        <v>3.316614420062695</v>
+        <v>0.1993769470404984</v>
       </c>
       <c r="AQ2">
-        <v>18.73394495412844</v>
+        <v>43.01639344262296</v>
       </c>
     </row>
     <row r="3">
@@ -707,7 +715,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The General Company for Ceramic and Porcelain Products (CASE:PRCL)</t>
+          <t>Macro Group Pharmaceuticals (Macro Capital) S.A.E (CASE:MCRO)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -715,113 +723,116 @@
           <t>Household Products</t>
         </is>
       </c>
-      <c r="D3">
-        <v>-0.0102</v>
-      </c>
       <c r="G3">
-        <v>-0.04202898550724637</v>
+        <v>0.3669467787114846</v>
       </c>
       <c r="H3">
-        <v>-0.04202898550724637</v>
+        <v>0.3669467787114846</v>
       </c>
       <c r="I3">
-        <v>-0.0927536231884058</v>
+        <v>0.3305322128851541</v>
       </c>
       <c r="J3">
-        <v>-0.0927536231884058</v>
+        <v>0.2522482677281438</v>
       </c>
       <c r="K3">
-        <v>-0.796</v>
+        <v>8.73</v>
       </c>
       <c r="L3">
-        <v>-0.05768115942028985</v>
+        <v>0.2445378151260504</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>4.8</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.06349206349206349</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>0.549828178694158</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>3.53</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.0466931216931217</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>0.404352806414662</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.27</v>
+      </c>
+      <c r="T3">
+        <v>0.2645833333333333</v>
       </c>
       <c r="U3">
-        <v>1.19</v>
+        <v>3.09</v>
       </c>
       <c r="V3">
-        <v>0.14</v>
+        <v>0.04087301587301587</v>
       </c>
       <c r="W3">
-        <v>-0.07171171171171171</v>
+        <v>0.4217391304347826</v>
       </c>
       <c r="X3">
-        <v>0.115858907697995</v>
+        <v>0.1972605454477098</v>
       </c>
       <c r="Y3">
-        <v>-0.1875706194097067</v>
+        <v>0.2244785849870728</v>
       </c>
       <c r="Z3">
-        <v>1.311413095124965</v>
+        <v>1.601686930773027</v>
       </c>
       <c r="AA3">
-        <v>-0.1216383160695619</v>
+        <v>0.4040227537303036</v>
       </c>
       <c r="AB3">
-        <v>0.1110840788282614</v>
+        <v>0.1889913929857192</v>
       </c>
       <c r="AC3">
-        <v>-0.2327223948978234</v>
+        <v>0.2150313607445843</v>
       </c>
       <c r="AD3">
-        <v>0.764</v>
+        <v>6.85</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.764</v>
+        <v>6.85</v>
       </c>
       <c r="AG3">
-        <v>-0.4259999999999999</v>
+        <v>3.76</v>
       </c>
       <c r="AH3">
-        <v>0.08246977547495683</v>
+        <v>0.08308065494238934</v>
       </c>
       <c r="AI3">
-        <v>0.07583879293230097</v>
+        <v>0.2424778761061947</v>
       </c>
       <c r="AJ3">
-        <v>-0.05276195194451325</v>
+        <v>0.04737903225806452</v>
       </c>
       <c r="AK3">
-        <v>-0.0479513732552904</v>
+        <v>0.1494435612082671</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.61</v>
       </c>
       <c r="AM3">
-        <v>-0.063</v>
+        <v>0.458</v>
       </c>
       <c r="AN3">
-        <v>-6.112</v>
+        <v>0.5756302521008403</v>
+      </c>
+      <c r="AO3">
+        <v>19.34426229508197</v>
       </c>
       <c r="AP3">
-        <v>3.407999999999999</v>
+        <v>0.3159663865546218</v>
       </c>
       <c r="AQ3">
-        <v>20.31746031746032</v>
+        <v>25.76419213973799</v>
       </c>
     </row>
     <row r="4">
@@ -841,28 +852,28 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.248</v>
+        <v>0.127</v>
       </c>
       <c r="E4">
-        <v>0.401</v>
+        <v>0.155</v>
       </c>
       <c r="G4">
-        <v>-0.005079207920792079</v>
+        <v>0.002152721364744111</v>
       </c>
       <c r="H4">
-        <v>-0.005079207920792079</v>
+        <v>0.002152721364744111</v>
       </c>
       <c r="I4">
-        <v>-0.007544554455445544</v>
+        <v>0.004435418359057677</v>
       </c>
       <c r="J4">
-        <v>-0.004248389887532442</v>
+        <v>0.00372855728237087</v>
       </c>
       <c r="K4">
-        <v>0.232</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L4">
-        <v>0.002297029702970297</v>
+        <v>0.005605199025182778</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -886,31 +897,31 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>1.69</v>
+        <v>1.23</v>
       </c>
       <c r="V4">
-        <v>0.1594339622641509</v>
+        <v>0.1898148148148148</v>
       </c>
       <c r="W4">
-        <v>0.07459807073954984</v>
+        <v>0.2011661807580175</v>
       </c>
       <c r="X4">
-        <v>0.1092972388593347</v>
+        <v>0.1868633087996893</v>
       </c>
       <c r="Y4">
-        <v>-0.03469916811978488</v>
+        <v>0.01430287195832816</v>
       </c>
       <c r="Z4">
-        <v>97.49034749034749</v>
+        <v>35.88921282798834</v>
       </c>
       <c r="AA4">
-        <v>-0.4141770064100161</v>
+        <v>0.1338149858483539</v>
       </c>
       <c r="AB4">
-        <v>0.1092972388593347</v>
+        <v>0.1868633087996893</v>
       </c>
       <c r="AC4">
-        <v>-0.5234742452693508</v>
+        <v>-0.05304832295133535</v>
       </c>
       <c r="AD4">
         <v>0</v>
@@ -922,7 +933,7 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>-1.69</v>
+        <v>-1.23</v>
       </c>
       <c r="AH4">
         <v>0</v>
@@ -931,25 +942,8862 @@
         <v>0</v>
       </c>
       <c r="AJ4">
-        <v>-0.1896745230078563</v>
+        <v>-0.2342857142857143</v>
       </c>
       <c r="AK4">
-        <v>-0.9712643678160918</v>
+        <v>-0.484251968503937</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-0.046</v>
+        <v>-0.17</v>
       </c>
       <c r="AN4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>-1.648793565683646</v>
+      </c>
+      <c r="AQ4">
+        <v>-3.211764705882353</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>The General Company for Ceramic and Porcelain Products (CASE:PRCL)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Household Products</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>-0.07679999999999999</v>
+      </c>
+      <c r="G5">
+        <v>-0.1028301886792453</v>
+      </c>
+      <c r="H5">
+        <v>-0.1028301886792453</v>
+      </c>
+      <c r="I5">
+        <v>-0.1745283018867925</v>
+      </c>
+      <c r="J5">
+        <v>-0.1745283018867925</v>
+      </c>
+      <c r="K5">
+        <v>-3.67</v>
+      </c>
+      <c r="L5">
+        <v>-0.3462264150943396</v>
+      </c>
+      <c r="M5">
         <v>-0</v>
       </c>
-      <c r="AP4">
-        <v>3.294346978557505</v>
-      </c>
-      <c r="AQ4">
-        <v>16.56521739130435</v>
+      <c r="N5">
+        <v>-0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>-0</v>
+      </c>
+      <c r="Q5">
+        <v>-0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0.581</v>
+      </c>
+      <c r="V5">
+        <v>0.07298994974874372</v>
+      </c>
+      <c r="W5">
+        <v>-0.6872659176029963</v>
+      </c>
+      <c r="X5">
+        <v>0.191980886416965</v>
+      </c>
+      <c r="Y5">
+        <v>-0.8792468040199612</v>
+      </c>
+      <c r="Z5">
+        <v>2.250530785562633</v>
+      </c>
+      <c r="AA5">
+        <v>-0.3927813163481954</v>
+      </c>
+      <c r="AB5">
+        <v>0.1878311663494354</v>
+      </c>
+      <c r="AC5">
+        <v>-0.5806124826976307</v>
+      </c>
+      <c r="AD5">
+        <v>0.355</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>0.355</v>
+      </c>
+      <c r="AG5">
+        <v>-0.226</v>
+      </c>
+      <c r="AH5">
+        <v>0.04269392663860493</v>
+      </c>
+      <c r="AI5">
+        <v>0.3103146853146853</v>
+      </c>
+      <c r="AJ5">
+        <v>-0.02922161882596327</v>
+      </c>
+      <c r="AK5">
+        <v>-0.4014209591474244</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>-0.044</v>
+      </c>
+      <c r="AN5">
+        <v>-0.3256880733944953</v>
+      </c>
+      <c r="AP5">
+        <v>0.2073394495412844</v>
+      </c>
+      <c r="AQ5">
+        <v>42.04545454545455</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Macro Group Pharmaceuticals (Macro Capital) S.A.E (CASE:MCRO)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>CASE:MCRO</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Household Products</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.0830806549423893</v>
+      </c>
+      <c r="F2">
+        <v>0.57</v>
+      </c>
+      <c r="G2">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="H2">
+        <v>46.9032965877846</v>
+      </c>
+      <c r="I2">
+        <v>79.36</v>
+      </c>
+      <c r="J2">
+        <v>90.8097965877846</v>
+      </c>
+      <c r="K2">
+        <v>6.85</v>
+      </c>
+      <c r="L2">
+        <v>46.9965</v>
+      </c>
+      <c r="M2">
+        <v>0.188991392985719</v>
+      </c>
+      <c r="N2">
+        <v>0.170054439446129</v>
+      </c>
+      <c r="O2">
+        <v>0.09772892201834869</v>
+      </c>
+      <c r="P2">
+        <v>0.042625</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.19726054544771</v>
+      </c>
+      <c r="T2">
+        <v>0.338972533595649</v>
+      </c>
+      <c r="U2">
+        <v>1.02843015151306</v>
+      </c>
+      <c r="V2">
+        <v>1.94815992418568</v>
+      </c>
+      <c r="W2">
+        <v>4.565136862222817</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="AB2">
+        <v>0.1540800269367614</v>
+      </c>
+      <c r="AC2">
+        <v>0.1261018348623854</v>
+      </c>
+      <c r="AD2">
+        <v>0.225</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>11.9</v>
+      </c>
+      <c r="AH2">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="AI2">
+        <v>0.395999999999999</v>
+      </c>
+      <c r="AJ2">
+        <v>6.85</v>
+      </c>
+      <c r="AK2">
+        <v>6.85</v>
+      </c>
+      <c r="AL2">
+        <v>0.61</v>
+      </c>
+      <c r="AM2">
+        <v>6.85</v>
+      </c>
+      <c r="AN2">
+        <v>3.09</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1868633087996893</v>
+      </c>
+      <c r="C2">
+        <v>83.59062533366597</v>
+      </c>
+      <c r="D2">
+        <v>80.50062533366597</v>
+      </c>
+      <c r="E2">
+        <v>-6.85</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>3.09</v>
+      </c>
+      <c r="H2">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>11.9</v>
+      </c>
+      <c r="K2">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L2">
+        <v>11.8</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>11.8</v>
+      </c>
+      <c r="O2">
+        <v>2.655</v>
+      </c>
+      <c r="P2">
+        <v>9.145000000000001</v>
+      </c>
+      <c r="Q2">
+        <v>9.245000000000001</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1868633087996893</v>
+      </c>
+      <c r="T2">
+        <v>0.9609506938914181</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.225</v>
+      </c>
+      <c r="W2">
+        <v>0.0354175</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.18649634135489</v>
+      </c>
+      <c r="C3">
+        <v>82.96613779512877</v>
+      </c>
+      <c r="D3">
+        <v>80.70063779512877</v>
+      </c>
+      <c r="E3">
+        <v>-6.0255</v>
+      </c>
+      <c r="F3">
+        <v>0.8244999999999999</v>
+      </c>
+      <c r="G3">
+        <v>3.09</v>
+      </c>
+      <c r="H3">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>11.9</v>
+      </c>
+      <c r="K3">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L3">
+        <v>11.8</v>
+      </c>
+      <c r="M3">
+        <v>0.03767965</v>
+      </c>
+      <c r="N3">
+        <v>11.76232035</v>
+      </c>
+      <c r="O3">
+        <v>2.64652207875</v>
+      </c>
+      <c r="P3">
+        <v>9.115798271250002</v>
+      </c>
+      <c r="Q3">
+        <v>9.215798271250002</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1880223902574646</v>
+      </c>
+      <c r="T3">
+        <v>0.9684732877072346</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.225</v>
+      </c>
+      <c r="W3">
+        <v>0.0354175</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>313.1663908767731</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1861293739100907</v>
+      </c>
+      <c r="C4">
+        <v>82.34264663714981</v>
+      </c>
+      <c r="D4">
+        <v>80.90164663714981</v>
+      </c>
+      <c r="E4">
+        <v>-5.201</v>
+      </c>
+      <c r="F4">
+        <v>1.649</v>
+      </c>
+      <c r="G4">
+        <v>3.09</v>
+      </c>
+      <c r="H4">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>11.9</v>
+      </c>
+      <c r="K4">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L4">
+        <v>11.8</v>
+      </c>
+      <c r="M4">
+        <v>0.0753593</v>
+      </c>
+      <c r="N4">
+        <v>11.7246407</v>
+      </c>
+      <c r="O4">
+        <v>2.6380441575</v>
+      </c>
+      <c r="P4">
+        <v>9.086596542500001</v>
+      </c>
+      <c r="Q4">
+        <v>9.1865965425</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.189205126438868</v>
+      </c>
+      <c r="T4">
+        <v>0.976149403845823</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.225</v>
+      </c>
+      <c r="W4">
+        <v>0.0354175</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>156.5831954383865</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1857624064652914</v>
+      </c>
+      <c r="C5">
+        <v>81.72015932366297</v>
+      </c>
+      <c r="D5">
+        <v>81.10365932366297</v>
+      </c>
+      <c r="E5">
+        <v>-4.3765</v>
+      </c>
+      <c r="F5">
+        <v>2.4735</v>
+      </c>
+      <c r="G5">
+        <v>3.09</v>
+      </c>
+      <c r="H5">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>11.9</v>
+      </c>
+      <c r="K5">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L5">
+        <v>11.8</v>
+      </c>
+      <c r="M5">
+        <v>0.11303895</v>
+      </c>
+      <c r="N5">
+        <v>11.68696105</v>
+      </c>
+      <c r="O5">
+        <v>2.62956623625</v>
+      </c>
+      <c r="P5">
+        <v>9.057394813750001</v>
+      </c>
+      <c r="Q5">
+        <v>9.157394813750001</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1904122489332901</v>
+      </c>
+      <c r="T5">
+        <v>0.9839837904202586</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.225</v>
+      </c>
+      <c r="W5">
+        <v>0.0354175</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>104.3887969589243</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.185395439020492</v>
+      </c>
+      <c r="C6">
+        <v>81.09868339333896</v>
+      </c>
+      <c r="D6">
+        <v>81.30668339333896</v>
+      </c>
+      <c r="E6">
+        <v>-3.552</v>
+      </c>
+      <c r="F6">
+        <v>3.298</v>
+      </c>
+      <c r="G6">
+        <v>3.09</v>
+      </c>
+      <c r="H6">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>11.9</v>
+      </c>
+      <c r="K6">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L6">
+        <v>11.8</v>
+      </c>
+      <c r="M6">
+        <v>0.1507186</v>
+      </c>
+      <c r="N6">
+        <v>11.6492814</v>
+      </c>
+      <c r="O6">
+        <v>2.621088315</v>
+      </c>
+      <c r="P6">
+        <v>9.028193085000002</v>
+      </c>
+      <c r="Q6">
+        <v>9.128193085000001</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1916445198130126</v>
+      </c>
+      <c r="T6">
+        <v>0.9919813933816617</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.225</v>
+      </c>
+      <c r="W6">
+        <v>0.0354175</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>78.29159771919326</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1850284715756927</v>
+      </c>
+      <c r="C7">
+        <v>80.47822646052315</v>
+      </c>
+      <c r="D7">
+        <v>81.51072646052314</v>
+      </c>
+      <c r="E7">
+        <v>-2.7275</v>
+      </c>
+      <c r="F7">
+        <v>4.1225</v>
+      </c>
+      <c r="G7">
+        <v>3.09</v>
+      </c>
+      <c r="H7">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>11.9</v>
+      </c>
+      <c r="K7">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L7">
+        <v>11.8</v>
+      </c>
+      <c r="M7">
+        <v>0.18839825</v>
+      </c>
+      <c r="N7">
+        <v>11.61160175</v>
+      </c>
+      <c r="O7">
+        <v>2.61261039375</v>
+      </c>
+      <c r="P7">
+        <v>8.99899135625</v>
+      </c>
+      <c r="Q7">
+        <v>9.09899135625</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1929027332375713</v>
+      </c>
+      <c r="T7">
+        <v>1.000147366931726</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0.225</v>
+      </c>
+      <c r="W7">
+        <v>0.0354175</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>62.6332781753546</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1846615041308934</v>
+      </c>
+      <c r="C8">
+        <v>79.85879621618749</v>
+      </c>
+      <c r="D8">
+        <v>81.71579621618748</v>
+      </c>
+      <c r="E8">
+        <v>-1.903</v>
+      </c>
+      <c r="F8">
+        <v>4.946999999999999</v>
+      </c>
+      <c r="G8">
+        <v>3.09</v>
+      </c>
+      <c r="H8">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>11.9</v>
+      </c>
+      <c r="K8">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L8">
+        <v>11.8</v>
+      </c>
+      <c r="M8">
+        <v>0.2260779</v>
+      </c>
+      <c r="N8">
+        <v>11.5739221</v>
+      </c>
+      <c r="O8">
+        <v>2.6041324725</v>
+      </c>
+      <c r="P8">
+        <v>8.969789627500001</v>
+      </c>
+      <c r="Q8">
+        <v>9.069789627500001</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1941877171605249</v>
+      </c>
+      <c r="T8">
+        <v>1.008487084599876</v>
+      </c>
+      <c r="U8">
+        <v>0.0457</v>
+      </c>
+      <c r="V8">
+        <v>0.225</v>
+      </c>
+      <c r="W8">
+        <v>0.0354175</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>52.19439847946217</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1842945366860942</v>
+      </c>
+      <c r="C9">
+        <v>79.24040042889676</v>
+      </c>
+      <c r="D9">
+        <v>81.92190042889676</v>
+      </c>
+      <c r="E9">
+        <v>-1.0785</v>
+      </c>
+      <c r="F9">
+        <v>5.7715</v>
+      </c>
+      <c r="G9">
+        <v>3.09</v>
+      </c>
+      <c r="H9">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>11.9</v>
+      </c>
+      <c r="K9">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L9">
+        <v>11.8</v>
+      </c>
+      <c r="M9">
+        <v>0.26375755</v>
+      </c>
+      <c r="N9">
+        <v>11.53624245</v>
+      </c>
+      <c r="O9">
+        <v>2.59565455125</v>
+      </c>
+      <c r="P9">
+        <v>8.940587898750001</v>
+      </c>
+      <c r="Q9">
+        <v>9.040587898750001</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1955003351463378</v>
+      </c>
+      <c r="T9">
+        <v>1.017006151035084</v>
+      </c>
+      <c r="U9">
+        <v>0.0457</v>
+      </c>
+      <c r="V9">
+        <v>0.225</v>
+      </c>
+      <c r="W9">
+        <v>0.0354175</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>44.73805583953901</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1839275692412949</v>
+      </c>
+      <c r="C10">
+        <v>78.62304694578985</v>
+      </c>
+      <c r="D10">
+        <v>82.12904694578985</v>
+      </c>
+      <c r="E10">
+        <v>-0.2540000000000004</v>
+      </c>
+      <c r="F10">
+        <v>6.595999999999999</v>
+      </c>
+      <c r="G10">
+        <v>3.09</v>
+      </c>
+      <c r="H10">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>11.9</v>
+      </c>
+      <c r="K10">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L10">
+        <v>11.8</v>
+      </c>
+      <c r="M10">
+        <v>0.3014372</v>
+      </c>
+      <c r="N10">
+        <v>11.4985628</v>
+      </c>
+      <c r="O10">
+        <v>2.58717663</v>
+      </c>
+      <c r="P10">
+        <v>8.91138617</v>
+      </c>
+      <c r="Q10">
+        <v>9.01138617</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1968414883057553</v>
+      </c>
+      <c r="T10">
+        <v>1.025710414566709</v>
+      </c>
+      <c r="U10">
+        <v>0.0457</v>
+      </c>
+      <c r="V10">
+        <v>0.225</v>
+      </c>
+      <c r="W10">
+        <v>0.0354175</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>39.14579885959662</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1835606017964956</v>
+      </c>
+      <c r="C11">
+        <v>78.00674369357532</v>
+      </c>
+      <c r="D11">
+        <v>82.33724369357532</v>
+      </c>
+      <c r="E11">
+        <v>0.5704999999999991</v>
+      </c>
+      <c r="F11">
+        <v>7.420499999999999</v>
+      </c>
+      <c r="G11">
+        <v>3.09</v>
+      </c>
+      <c r="H11">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>11.9</v>
+      </c>
+      <c r="K11">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L11">
+        <v>11.8</v>
+      </c>
+      <c r="M11">
+        <v>0.33911685</v>
+      </c>
+      <c r="N11">
+        <v>11.46088315</v>
+      </c>
+      <c r="O11">
+        <v>2.57869870875</v>
+      </c>
+      <c r="P11">
+        <v>8.882184441250001</v>
+      </c>
+      <c r="Q11">
+        <v>8.98218444125</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1982121173587864</v>
+      </c>
+      <c r="T11">
+        <v>1.034605980593535</v>
+      </c>
+      <c r="U11">
+        <v>0.0457</v>
+      </c>
+      <c r="V11">
+        <v>0.225</v>
+      </c>
+      <c r="W11">
+        <v>0.0354175</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>34.79626565297478</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1831936343516963</v>
+      </c>
+      <c r="C12">
+        <v>77.39149867954274</v>
+      </c>
+      <c r="D12">
+        <v>82.54649867954274</v>
+      </c>
+      <c r="E12">
+        <v>1.395</v>
+      </c>
+      <c r="F12">
+        <v>8.244999999999999</v>
+      </c>
+      <c r="G12">
+        <v>3.09</v>
+      </c>
+      <c r="H12">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>11.9</v>
+      </c>
+      <c r="K12">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L12">
+        <v>11.8</v>
+      </c>
+      <c r="M12">
+        <v>0.3767965</v>
+      </c>
+      <c r="N12">
+        <v>11.4232035</v>
+      </c>
+      <c r="O12">
+        <v>2.5702207875</v>
+      </c>
+      <c r="P12">
+        <v>8.852982712500001</v>
+      </c>
+      <c r="Q12">
+        <v>8.952982712500001</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1996132048352181</v>
+      </c>
+      <c r="T12">
+        <v>1.043699225865401</v>
+      </c>
+      <c r="U12">
+        <v>0.0457</v>
+      </c>
+      <c r="V12">
+        <v>0.225</v>
+      </c>
+      <c r="W12">
+        <v>0.0354175</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>31.31663908767731</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1828266669068969</v>
+      </c>
+      <c r="C13">
+        <v>76.7773199925892</v>
+      </c>
+      <c r="D13">
+        <v>82.7568199925892</v>
+      </c>
+      <c r="E13">
+        <v>2.2195</v>
+      </c>
+      <c r="F13">
+        <v>9.0695</v>
+      </c>
+      <c r="G13">
+        <v>3.09</v>
+      </c>
+      <c r="H13">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>11.9</v>
+      </c>
+      <c r="K13">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L13">
+        <v>11.8</v>
+      </c>
+      <c r="M13">
+        <v>0.41447615</v>
+      </c>
+      <c r="N13">
+        <v>11.38552385</v>
+      </c>
+      <c r="O13">
+        <v>2.56174286625</v>
+      </c>
+      <c r="P13">
+        <v>8.82378098375</v>
+      </c>
+      <c r="Q13">
+        <v>8.92378098375</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.2010457774234797</v>
+      </c>
+      <c r="T13">
+        <v>1.052996813727646</v>
+      </c>
+      <c r="U13">
+        <v>0.0457</v>
+      </c>
+      <c r="V13">
+        <v>0.225</v>
+      </c>
+      <c r="W13">
+        <v>0.0354175</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>28.46967189788845</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1824596994620977</v>
+      </c>
+      <c r="C14">
+        <v>76.16421580426154</v>
+      </c>
+      <c r="D14">
+        <v>82.96821580426153</v>
+      </c>
+      <c r="E14">
+        <v>3.043999999999999</v>
+      </c>
+      <c r="F14">
+        <v>9.893999999999998</v>
+      </c>
+      <c r="G14">
+        <v>3.09</v>
+      </c>
+      <c r="H14">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>11.9</v>
+      </c>
+      <c r="K14">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L14">
+        <v>11.8</v>
+      </c>
+      <c r="M14">
+        <v>0.4521558</v>
+      </c>
+      <c r="N14">
+        <v>11.3478442</v>
+      </c>
+      <c r="O14">
+        <v>2.553264945</v>
+      </c>
+      <c r="P14">
+        <v>8.794579255</v>
+      </c>
+      <c r="Q14">
+        <v>8.894579255</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.2025109084796564</v>
+      </c>
+      <c r="T14">
+        <v>1.062505710404943</v>
+      </c>
+      <c r="U14">
+        <v>0.0457</v>
+      </c>
+      <c r="V14">
+        <v>0.225</v>
+      </c>
+      <c r="W14">
+        <v>0.0354175</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>26.09719923973109</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1820927320172984</v>
+      </c>
+      <c r="C15">
+        <v>75.5521943698148</v>
+      </c>
+      <c r="D15">
+        <v>83.1806943698148</v>
+      </c>
+      <c r="E15">
+        <v>3.868499999999999</v>
+      </c>
+      <c r="F15">
+        <v>10.7185</v>
+      </c>
+      <c r="G15">
+        <v>3.09</v>
+      </c>
+      <c r="H15">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>11.9</v>
+      </c>
+      <c r="K15">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L15">
+        <v>11.8</v>
+      </c>
+      <c r="M15">
+        <v>0.48983545</v>
+      </c>
+      <c r="N15">
+        <v>11.31016455</v>
+      </c>
+      <c r="O15">
+        <v>2.54478702375</v>
+      </c>
+      <c r="P15">
+        <v>8.765377526250001</v>
+      </c>
+      <c r="Q15">
+        <v>8.865377526250001</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.2040097207095384</v>
+      </c>
+      <c r="T15">
+        <v>1.072233202408154</v>
+      </c>
+      <c r="U15">
+        <v>0.0457</v>
+      </c>
+      <c r="V15">
+        <v>0.225</v>
+      </c>
+      <c r="W15">
+        <v>0.0354175</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>24.08972237513639</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1817257645724991</v>
+      </c>
+      <c r="C16">
+        <v>74.9412640292868</v>
+      </c>
+      <c r="D16">
+        <v>83.3942640292868</v>
+      </c>
+      <c r="E16">
+        <v>4.693</v>
+      </c>
+      <c r="F16">
+        <v>11.543</v>
+      </c>
+      <c r="G16">
+        <v>3.09</v>
+      </c>
+      <c r="H16">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>11.9</v>
+      </c>
+      <c r="K16">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L16">
+        <v>11.8</v>
+      </c>
+      <c r="M16">
+        <v>0.5275151</v>
+      </c>
+      <c r="N16">
+        <v>11.2724849</v>
+      </c>
+      <c r="O16">
+        <v>2.5363091025</v>
+      </c>
+      <c r="P16">
+        <v>8.7361757975</v>
+      </c>
+      <c r="Q16">
+        <v>8.836175797499999</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.2055433890377896</v>
+      </c>
+      <c r="T16">
+        <v>1.082186915155626</v>
+      </c>
+      <c r="U16">
+        <v>0.0457</v>
+      </c>
+      <c r="V16">
+        <v>0.225</v>
+      </c>
+      <c r="W16">
+        <v>0.0354175</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>22.3690279197695</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1813587971276998</v>
+      </c>
+      <c r="C17">
+        <v>74.33143320858925</v>
+      </c>
+      <c r="D17">
+        <v>83.60893320858924</v>
+      </c>
+      <c r="E17">
+        <v>5.517499999999998</v>
+      </c>
+      <c r="F17">
+        <v>12.3675</v>
+      </c>
+      <c r="G17">
+        <v>3.09</v>
+      </c>
+      <c r="H17">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>11.9</v>
+      </c>
+      <c r="K17">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L17">
+        <v>11.8</v>
+      </c>
+      <c r="M17">
+        <v>0.56519475</v>
+      </c>
+      <c r="N17">
+        <v>11.23480525</v>
+      </c>
+      <c r="O17">
+        <v>2.52783118125</v>
+      </c>
+      <c r="P17">
+        <v>8.70697406875</v>
+      </c>
+      <c r="Q17">
+        <v>8.80697406875</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.2071131436796468</v>
+      </c>
+      <c r="T17">
+        <v>1.092374832908921</v>
+      </c>
+      <c r="U17">
+        <v>0.0457</v>
+      </c>
+      <c r="V17">
+        <v>0.225</v>
+      </c>
+      <c r="W17">
+        <v>0.0354175</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>20.87775939178487</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1809918296829005</v>
+      </c>
+      <c r="C18">
+        <v>73.72271042061597</v>
+      </c>
+      <c r="D18">
+        <v>83.82471042061596</v>
+      </c>
+      <c r="E18">
+        <v>6.341999999999999</v>
+      </c>
+      <c r="F18">
+        <v>13.192</v>
+      </c>
+      <c r="G18">
+        <v>3.09</v>
+      </c>
+      <c r="H18">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>11.9</v>
+      </c>
+      <c r="K18">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L18">
+        <v>11.8</v>
+      </c>
+      <c r="M18">
+        <v>0.6028744</v>
+      </c>
+      <c r="N18">
+        <v>11.1971256</v>
+      </c>
+      <c r="O18">
+        <v>2.51935326</v>
+      </c>
+      <c r="P18">
+        <v>8.677772340000001</v>
+      </c>
+      <c r="Q18">
+        <v>8.77777234</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.2087202734320243</v>
+      </c>
+      <c r="T18">
+        <v>1.102805320132532</v>
+      </c>
+      <c r="U18">
+        <v>0.0457</v>
+      </c>
+      <c r="V18">
+        <v>0.225</v>
+      </c>
+      <c r="W18">
+        <v>0.0354175</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>19.57289942979832</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1806248622381011</v>
+      </c>
+      <c r="C19">
+        <v>73.11510426636814</v>
+      </c>
+      <c r="D19">
+        <v>84.04160426636813</v>
+      </c>
+      <c r="E19">
+        <v>7.166499999999999</v>
+      </c>
+      <c r="F19">
+        <v>14.0165</v>
+      </c>
+      <c r="G19">
+        <v>3.09</v>
+      </c>
+      <c r="H19">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>11.9</v>
+      </c>
+      <c r="K19">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L19">
+        <v>11.8</v>
+      </c>
+      <c r="M19">
+        <v>0.64055405</v>
+      </c>
+      <c r="N19">
+        <v>11.15944595</v>
+      </c>
+      <c r="O19">
+        <v>2.51087533875</v>
+      </c>
+      <c r="P19">
+        <v>8.648570611250001</v>
+      </c>
+      <c r="Q19">
+        <v>8.748570611250001</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.2103661292025315</v>
+      </c>
+      <c r="T19">
+        <v>1.113487144397676</v>
+      </c>
+      <c r="U19">
+        <v>0.0457</v>
+      </c>
+      <c r="V19">
+        <v>0.225</v>
+      </c>
+      <c r="W19">
+        <v>0.0354175</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>18.42155240451606</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1802578947933019</v>
+      </c>
+      <c r="C20">
+        <v>72.50862343609724</v>
+      </c>
+      <c r="D20">
+        <v>84.25962343609723</v>
+      </c>
+      <c r="E20">
+        <v>7.990999999999998</v>
+      </c>
+      <c r="F20">
+        <v>14.841</v>
+      </c>
+      <c r="G20">
+        <v>3.09</v>
+      </c>
+      <c r="H20">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>11.9</v>
+      </c>
+      <c r="K20">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L20">
+        <v>11.8</v>
+      </c>
+      <c r="M20">
+        <v>0.6782336999999999</v>
+      </c>
+      <c r="N20">
+        <v>11.1217663</v>
+      </c>
+      <c r="O20">
+        <v>2.5023974175</v>
+      </c>
+      <c r="P20">
+        <v>8.619368882500002</v>
+      </c>
+      <c r="Q20">
+        <v>8.719368882500001</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.2120521277967096</v>
+      </c>
+      <c r="T20">
+        <v>1.12442950096197</v>
+      </c>
+      <c r="U20">
+        <v>0.0457</v>
+      </c>
+      <c r="V20">
+        <v>0.225</v>
+      </c>
+      <c r="W20">
+        <v>0.0354175</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>17.39813282648739</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1798909273485026</v>
+      </c>
+      <c r="C21">
+        <v>71.90327671046562</v>
+      </c>
+      <c r="D21">
+        <v>84.47877671046561</v>
+      </c>
+      <c r="E21">
+        <v>8.815499999999998</v>
+      </c>
+      <c r="F21">
+        <v>15.6655</v>
+      </c>
+      <c r="G21">
+        <v>3.09</v>
+      </c>
+      <c r="H21">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>11.9</v>
+      </c>
+      <c r="K21">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L21">
+        <v>11.8</v>
+      </c>
+      <c r="M21">
+        <v>0.71591335</v>
+      </c>
+      <c r="N21">
+        <v>11.08408665</v>
+      </c>
+      <c r="O21">
+        <v>2.49391949625</v>
+      </c>
+      <c r="P21">
+        <v>8.590167153750002</v>
+      </c>
+      <c r="Q21">
+        <v>8.690167153750002</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.2137797559858056</v>
+      </c>
+      <c r="T21">
+        <v>1.135642039169827</v>
+      </c>
+      <c r="U21">
+        <v>0.0457</v>
+      </c>
+      <c r="V21">
+        <v>0.225</v>
+      </c>
+      <c r="W21">
+        <v>0.0354175</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>16.48244162509332</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1795239599037033</v>
+      </c>
+      <c r="C22">
+        <v>71.29907296172536</v>
+      </c>
+      <c r="D22">
+        <v>84.69907296172535</v>
+      </c>
+      <c r="E22">
+        <v>9.639999999999999</v>
+      </c>
+      <c r="F22">
+        <v>16.49</v>
+      </c>
+      <c r="G22">
+        <v>3.09</v>
+      </c>
+      <c r="H22">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>11.9</v>
+      </c>
+      <c r="K22">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L22">
+        <v>11.8</v>
+      </c>
+      <c r="M22">
+        <v>0.753593</v>
+      </c>
+      <c r="N22">
+        <v>11.046407</v>
+      </c>
+      <c r="O22">
+        <v>2.485441575</v>
+      </c>
+      <c r="P22">
+        <v>8.560965425000001</v>
+      </c>
+      <c r="Q22">
+        <v>8.660965425000001</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.2155505748796291</v>
+      </c>
+      <c r="T22">
+        <v>1.14713489083288</v>
+      </c>
+      <c r="U22">
+        <v>0.0457</v>
+      </c>
+      <c r="V22">
+        <v>0.225</v>
+      </c>
+      <c r="W22">
+        <v>0.0354175</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>15.65831954383865</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.179156992458904</v>
+      </c>
+      <c r="C23">
+        <v>70.69602115491553</v>
+      </c>
+      <c r="D23">
+        <v>84.92052115491552</v>
+      </c>
+      <c r="E23">
+        <v>10.4645</v>
+      </c>
+      <c r="F23">
+        <v>17.3145</v>
+      </c>
+      <c r="G23">
+        <v>3.09</v>
+      </c>
+      <c r="H23">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>11.9</v>
+      </c>
+      <c r="K23">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L23">
+        <v>11.8</v>
+      </c>
+      <c r="M23">
+        <v>0.7912726499999999</v>
+      </c>
+      <c r="N23">
+        <v>11.00872735</v>
+      </c>
+      <c r="O23">
+        <v>2.47696365375</v>
+      </c>
+      <c r="P23">
+        <v>8.531763696250001</v>
+      </c>
+      <c r="Q23">
+        <v>8.631763696250001</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.217366224631524</v>
+      </c>
+      <c r="T23">
+        <v>1.158918700765884</v>
+      </c>
+      <c r="U23">
+        <v>0.0457</v>
+      </c>
+      <c r="V23">
+        <v>0.225</v>
+      </c>
+      <c r="W23">
+        <v>0.0354175</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>14.91268527984634</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1787900250141047</v>
+      </c>
+      <c r="C24">
+        <v>70.09413034907853</v>
+      </c>
+      <c r="D24">
+        <v>85.14313034907852</v>
+      </c>
+      <c r="E24">
+        <v>11.289</v>
+      </c>
+      <c r="F24">
+        <v>18.139</v>
+      </c>
+      <c r="G24">
+        <v>3.09</v>
+      </c>
+      <c r="H24">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>11.9</v>
+      </c>
+      <c r="K24">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L24">
+        <v>11.8</v>
+      </c>
+      <c r="M24">
+        <v>0.8289523000000001</v>
+      </c>
+      <c r="N24">
+        <v>10.9710477</v>
+      </c>
+      <c r="O24">
+        <v>2.4684857325</v>
+      </c>
+      <c r="P24">
+        <v>8.5025619675</v>
+      </c>
+      <c r="Q24">
+        <v>8.6025619675</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.2192284295052624</v>
+      </c>
+      <c r="T24">
+        <v>1.171004659671529</v>
+      </c>
+      <c r="U24">
+        <v>0.0457</v>
+      </c>
+      <c r="V24">
+        <v>0.225</v>
+      </c>
+      <c r="W24">
+        <v>0.0354175</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>14.23483594894423</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1784230575693053</v>
+      </c>
+      <c r="C25">
+        <v>69.49340969849511</v>
+      </c>
+      <c r="D25">
+        <v>85.36690969849511</v>
+      </c>
+      <c r="E25">
+        <v>12.1135</v>
+      </c>
+      <c r="F25">
+        <v>18.9635</v>
+      </c>
+      <c r="G25">
+        <v>3.09</v>
+      </c>
+      <c r="H25">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>11.9</v>
+      </c>
+      <c r="K25">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L25">
+        <v>11.8</v>
+      </c>
+      <c r="M25">
+        <v>0.86663195</v>
+      </c>
+      <c r="N25">
+        <v>10.93336805</v>
+      </c>
+      <c r="O25">
+        <v>2.46000781125</v>
+      </c>
+      <c r="P25">
+        <v>8.473360238750001</v>
+      </c>
+      <c r="Q25">
+        <v>8.57336023875</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.2211390033367602</v>
+      </c>
+      <c r="T25">
+        <v>1.183404539587711</v>
+      </c>
+      <c r="U25">
+        <v>0.0457</v>
+      </c>
+      <c r="V25">
+        <v>0.225</v>
+      </c>
+      <c r="W25">
+        <v>0.0354175</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>13.61593003812057</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1780560901245061</v>
+      </c>
+      <c r="C26">
+        <v>68.89386845393956</v>
+      </c>
+      <c r="D26">
+        <v>85.59186845393955</v>
+      </c>
+      <c r="E26">
+        <v>12.938</v>
+      </c>
+      <c r="F26">
+        <v>19.788</v>
+      </c>
+      <c r="G26">
+        <v>3.09</v>
+      </c>
+      <c r="H26">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>11.9</v>
+      </c>
+      <c r="K26">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L26">
+        <v>11.8</v>
+      </c>
+      <c r="M26">
+        <v>0.9043116</v>
+      </c>
+      <c r="N26">
+        <v>10.8956884</v>
+      </c>
+      <c r="O26">
+        <v>2.45152989</v>
+      </c>
+      <c r="P26">
+        <v>8.444158510000001</v>
+      </c>
+      <c r="Q26">
+        <v>8.544158510000001</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.2230998554269817</v>
+      </c>
+      <c r="T26">
+        <v>1.196130732133265</v>
+      </c>
+      <c r="U26">
+        <v>0.0457</v>
+      </c>
+      <c r="V26">
+        <v>0.225</v>
+      </c>
+      <c r="W26">
+        <v>0.0354175</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>13.04859961986554</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1779991226797067</v>
+      </c>
+      <c r="C27">
+        <v>68.10439705144474</v>
+      </c>
+      <c r="D27">
+        <v>85.62689705144473</v>
+      </c>
+      <c r="E27">
+        <v>13.7625</v>
+      </c>
+      <c r="F27">
+        <v>20.6125</v>
+      </c>
+      <c r="G27">
+        <v>3.09</v>
+      </c>
+      <c r="H27">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>11.9</v>
+      </c>
+      <c r="K27">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L27">
+        <v>11.8</v>
+      </c>
+      <c r="M27">
+        <v>0.97497125</v>
+      </c>
+      <c r="N27">
+        <v>10.82502875</v>
+      </c>
+      <c r="O27">
+        <v>2.43563146875</v>
+      </c>
+      <c r="P27">
+        <v>8.389397281250002</v>
+      </c>
+      <c r="Q27">
+        <v>8.489397281250001</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.2251129969062757</v>
+      </c>
+      <c r="T27">
+        <v>1.209196289813368</v>
+      </c>
+      <c r="U27">
+        <v>0.0473</v>
+      </c>
+      <c r="V27">
+        <v>0.225</v>
+      </c>
+      <c r="W27">
+        <v>0.0366575</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>12.10292098356747</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1776445552349075</v>
+      </c>
+      <c r="C28">
+        <v>67.49856252264203</v>
+      </c>
+      <c r="D28">
+        <v>85.84556252264203</v>
+      </c>
+      <c r="E28">
+        <v>14.587</v>
+      </c>
+      <c r="F28">
+        <v>21.437</v>
+      </c>
+      <c r="G28">
+        <v>3.09</v>
+      </c>
+      <c r="H28">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>11.9</v>
+      </c>
+      <c r="K28">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L28">
+        <v>11.8</v>
+      </c>
+      <c r="M28">
+        <v>1.0139701</v>
+      </c>
+      <c r="N28">
+        <v>10.7860299</v>
+      </c>
+      <c r="O28">
+        <v>2.4268567275</v>
+      </c>
+      <c r="P28">
+        <v>8.3591731725</v>
+      </c>
+      <c r="Q28">
+        <v>8.4591731725</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.2271805476147399</v>
+      </c>
+      <c r="T28">
+        <v>1.222614970674014</v>
+      </c>
+      <c r="U28">
+        <v>0.0473</v>
+      </c>
+      <c r="V28">
+        <v>0.225</v>
+      </c>
+      <c r="W28">
+        <v>0.0366575</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>11.63742402266103</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1772899877901082</v>
+      </c>
+      <c r="C29">
+        <v>66.8938476655012</v>
+      </c>
+      <c r="D29">
+        <v>86.06534766550119</v>
+      </c>
+      <c r="E29">
+        <v>15.4115</v>
+      </c>
+      <c r="F29">
+        <v>22.2615</v>
+      </c>
+      <c r="G29">
+        <v>3.09</v>
+      </c>
+      <c r="H29">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>11.9</v>
+      </c>
+      <c r="K29">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L29">
+        <v>11.8</v>
+      </c>
+      <c r="M29">
+        <v>1.05296895</v>
+      </c>
+      <c r="N29">
+        <v>10.74703105</v>
+      </c>
+      <c r="O29">
+        <v>2.41808198625</v>
+      </c>
+      <c r="P29">
+        <v>8.328949063750001</v>
+      </c>
+      <c r="Q29">
+        <v>8.42894906375</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.2293047435480934</v>
+      </c>
+      <c r="T29">
+        <v>1.236401286626732</v>
+      </c>
+      <c r="U29">
+        <v>0.0473</v>
+      </c>
+      <c r="V29">
+        <v>0.225</v>
+      </c>
+      <c r="W29">
+        <v>0.0366575</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>11.20640831811802</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1769354203453088</v>
+      </c>
+      <c r="C30">
+        <v>66.29026110197707</v>
+      </c>
+      <c r="D30">
+        <v>86.28626110197706</v>
+      </c>
+      <c r="E30">
+        <v>16.236</v>
+      </c>
+      <c r="F30">
+        <v>23.086</v>
+      </c>
+      <c r="G30">
+        <v>3.09</v>
+      </c>
+      <c r="H30">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>11.9</v>
+      </c>
+      <c r="K30">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L30">
+        <v>11.8</v>
+      </c>
+      <c r="M30">
+        <v>1.0919678</v>
+      </c>
+      <c r="N30">
+        <v>10.7080322</v>
+      </c>
+      <c r="O30">
+        <v>2.409307245</v>
+      </c>
+      <c r="P30">
+        <v>8.298724955000001</v>
+      </c>
+      <c r="Q30">
+        <v>8.398724955</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.2314879449240401</v>
+      </c>
+      <c r="T30">
+        <v>1.250570555800359</v>
+      </c>
+      <c r="U30">
+        <v>0.0473</v>
+      </c>
+      <c r="V30">
+        <v>0.225</v>
+      </c>
+      <c r="W30">
+        <v>0.0366575</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>10.80617944961381</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1765808529005095</v>
+      </c>
+      <c r="C31">
+        <v>65.68781154277603</v>
+      </c>
+      <c r="D31">
+        <v>86.50831154277603</v>
+      </c>
+      <c r="E31">
+        <v>17.0605</v>
+      </c>
+      <c r="F31">
+        <v>23.9105</v>
+      </c>
+      <c r="G31">
+        <v>3.09</v>
+      </c>
+      <c r="H31">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>11.9</v>
+      </c>
+      <c r="K31">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L31">
+        <v>11.8</v>
+      </c>
+      <c r="M31">
+        <v>1.13096665</v>
+      </c>
+      <c r="N31">
+        <v>10.66903335</v>
+      </c>
+      <c r="O31">
+        <v>2.40053250375</v>
+      </c>
+      <c r="P31">
+        <v>8.268500846250001</v>
+      </c>
+      <c r="Q31">
+        <v>8.368500846250001</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.2337326449302951</v>
+      </c>
+      <c r="T31">
+        <v>1.265138959316906</v>
+      </c>
+      <c r="U31">
+        <v>0.0473</v>
+      </c>
+      <c r="V31">
+        <v>0.225</v>
+      </c>
+      <c r="W31">
+        <v>0.0366575</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>10.43355257204092</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1771097854557102</v>
+      </c>
+      <c r="C32">
+        <v>64.53248128286594</v>
+      </c>
+      <c r="D32">
+        <v>86.17748128286594</v>
+      </c>
+      <c r="E32">
+        <v>17.885</v>
+      </c>
+      <c r="F32">
+        <v>24.735</v>
+      </c>
+      <c r="G32">
+        <v>3.09</v>
+      </c>
+      <c r="H32">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>11.9</v>
+      </c>
+      <c r="K32">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L32">
+        <v>11.8</v>
+      </c>
+      <c r="M32">
+        <v>1.2639585</v>
+      </c>
+      <c r="N32">
+        <v>10.5360415</v>
+      </c>
+      <c r="O32">
+        <v>2.3706093375</v>
+      </c>
+      <c r="P32">
+        <v>8.165432162500002</v>
+      </c>
+      <c r="Q32">
+        <v>8.265432162500002</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.2360414792224432</v>
+      </c>
+      <c r="T32">
+        <v>1.280123602933925</v>
+      </c>
+      <c r="U32">
+        <v>0.0511</v>
+      </c>
+      <c r="V32">
+        <v>0.225</v>
+      </c>
+      <c r="W32">
+        <v>0.0396025</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>9.335749551903803</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1767846680109109</v>
+      </c>
+      <c r="C33">
+        <v>63.91103139646054</v>
+      </c>
+      <c r="D33">
+        <v>86.38053139646054</v>
+      </c>
+      <c r="E33">
+        <v>18.7095</v>
+      </c>
+      <c r="F33">
+        <v>25.5595</v>
+      </c>
+      <c r="G33">
+        <v>3.09</v>
+      </c>
+      <c r="H33">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>11.9</v>
+      </c>
+      <c r="K33">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L33">
+        <v>11.8</v>
+      </c>
+      <c r="M33">
+        <v>1.30609045</v>
+      </c>
+      <c r="N33">
+        <v>10.49390955</v>
+      </c>
+      <c r="O33">
+        <v>2.36112964875</v>
+      </c>
+      <c r="P33">
+        <v>8.132779901250002</v>
+      </c>
+      <c r="Q33">
+        <v>8.232779901250002</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.238417236247697</v>
+      </c>
+      <c r="T33">
+        <v>1.295542584047089</v>
+      </c>
+      <c r="U33">
+        <v>0.0511</v>
+      </c>
+      <c r="V33">
+        <v>0.225</v>
+      </c>
+      <c r="W33">
+        <v>0.0396025</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>9.034596340552067</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1764595505661117</v>
+      </c>
+      <c r="C34">
+        <v>63.29054061727034</v>
+      </c>
+      <c r="D34">
+        <v>86.58454061727033</v>
+      </c>
+      <c r="E34">
+        <v>19.534</v>
+      </c>
+      <c r="F34">
+        <v>26.384</v>
+      </c>
+      <c r="G34">
+        <v>3.09</v>
+      </c>
+      <c r="H34">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>11.9</v>
+      </c>
+      <c r="K34">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L34">
+        <v>11.8</v>
+      </c>
+      <c r="M34">
+        <v>1.3482224</v>
+      </c>
+      <c r="N34">
+        <v>10.4517776</v>
+      </c>
+      <c r="O34">
+        <v>2.35164996</v>
+      </c>
+      <c r="P34">
+        <v>8.100127640000002</v>
+      </c>
+      <c r="Q34">
+        <v>8.200127640000002</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.240862868479576</v>
+      </c>
+      <c r="T34">
+        <v>1.311415064604759</v>
+      </c>
+      <c r="U34">
+        <v>0.0511</v>
+      </c>
+      <c r="V34">
+        <v>0.225</v>
+      </c>
+      <c r="W34">
+        <v>0.0396025</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>8.752265204909815</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1761344331213124</v>
+      </c>
+      <c r="C35">
+        <v>62.67101575689712</v>
+      </c>
+      <c r="D35">
+        <v>86.78951575689712</v>
+      </c>
+      <c r="E35">
+        <v>20.3585</v>
+      </c>
+      <c r="F35">
+        <v>27.2085</v>
+      </c>
+      <c r="G35">
+        <v>3.09</v>
+      </c>
+      <c r="H35">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>11.9</v>
+      </c>
+      <c r="K35">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L35">
+        <v>11.8</v>
+      </c>
+      <c r="M35">
+        <v>1.39035435</v>
+      </c>
+      <c r="N35">
+        <v>10.40964565</v>
+      </c>
+      <c r="O35">
+        <v>2.34217027125</v>
+      </c>
+      <c r="P35">
+        <v>8.067475378750002</v>
+      </c>
+      <c r="Q35">
+        <v>8.167475378750002</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.2433815046586752</v>
+      </c>
+      <c r="T35">
+        <v>1.32776135055221</v>
+      </c>
+      <c r="U35">
+        <v>0.0511</v>
+      </c>
+      <c r="V35">
+        <v>0.225</v>
+      </c>
+      <c r="W35">
+        <v>0.0396025</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>8.487045047185276</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1758093156765131</v>
+      </c>
+      <c r="C36">
+        <v>62.05246369159723</v>
+      </c>
+      <c r="D36">
+        <v>86.99546369159722</v>
+      </c>
+      <c r="E36">
+        <v>21.183</v>
+      </c>
+      <c r="F36">
+        <v>28.033</v>
+      </c>
+      <c r="G36">
+        <v>3.09</v>
+      </c>
+      <c r="H36">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>11.9</v>
+      </c>
+      <c r="K36">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L36">
+        <v>11.8</v>
+      </c>
+      <c r="M36">
+        <v>1.4324863</v>
+      </c>
+      <c r="N36">
+        <v>10.3675137</v>
+      </c>
+      <c r="O36">
+        <v>2.3326905825</v>
+      </c>
+      <c r="P36">
+        <v>8.0348231175</v>
+      </c>
+      <c r="Q36">
+        <v>8.1348231175</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.2459764631462319</v>
+      </c>
+      <c r="T36">
+        <v>1.344602978498068</v>
+      </c>
+      <c r="U36">
+        <v>0.0511</v>
+      </c>
+      <c r="V36">
+        <v>0.225</v>
+      </c>
+      <c r="W36">
+        <v>0.0396025</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>8.237426075209235</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1754841982317137</v>
+      </c>
+      <c r="C37">
+        <v>61.43489136305048</v>
+      </c>
+      <c r="D37">
+        <v>87.20239136305048</v>
+      </c>
+      <c r="E37">
+        <v>22.0075</v>
+      </c>
+      <c r="F37">
+        <v>28.8575</v>
+      </c>
+      <c r="G37">
+        <v>3.09</v>
+      </c>
+      <c r="H37">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>11.9</v>
+      </c>
+      <c r="K37">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L37">
+        <v>11.8</v>
+      </c>
+      <c r="M37">
+        <v>1.47461825</v>
+      </c>
+      <c r="N37">
+        <v>10.32538175</v>
+      </c>
+      <c r="O37">
+        <v>2.32321089375</v>
+      </c>
+      <c r="P37">
+        <v>8.002170856250002</v>
+      </c>
+      <c r="Q37">
+        <v>8.102170856250002</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.2486512665103289</v>
+      </c>
+      <c r="T37">
+        <v>1.361962810380722</v>
+      </c>
+      <c r="U37">
+        <v>0.0511</v>
+      </c>
+      <c r="V37">
+        <v>0.225</v>
+      </c>
+      <c r="W37">
+        <v>0.0396025</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>8.002071044488975</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1751590807869144</v>
+      </c>
+      <c r="C38">
+        <v>60.81830577914022</v>
+      </c>
+      <c r="D38">
+        <v>87.41030577914022</v>
+      </c>
+      <c r="E38">
+        <v>22.83199999999999</v>
+      </c>
+      <c r="F38">
+        <v>29.682</v>
+      </c>
+      <c r="G38">
+        <v>3.09</v>
+      </c>
+      <c r="H38">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>11.9</v>
+      </c>
+      <c r="K38">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L38">
+        <v>11.8</v>
+      </c>
+      <c r="M38">
+        <v>1.5167502</v>
+      </c>
+      <c r="N38">
+        <v>10.2832498</v>
+      </c>
+      <c r="O38">
+        <v>2.313731205</v>
+      </c>
+      <c r="P38">
+        <v>7.969518595</v>
+      </c>
+      <c r="Q38">
+        <v>8.069518595</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.2514096574795538</v>
+      </c>
+      <c r="T38">
+        <v>1.379865137009708</v>
+      </c>
+      <c r="U38">
+        <v>0.0511</v>
+      </c>
+      <c r="V38">
+        <v>0.225</v>
+      </c>
+      <c r="W38">
+        <v>0.0396025</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>7.779791293253169</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1753787883421152</v>
+      </c>
+      <c r="C39">
+        <v>59.8531931348548</v>
+      </c>
+      <c r="D39">
+        <v>87.26969313485479</v>
+      </c>
+      <c r="E39">
+        <v>23.65649999999999</v>
+      </c>
+      <c r="F39">
+        <v>30.5065</v>
+      </c>
+      <c r="G39">
+        <v>3.09</v>
+      </c>
+      <c r="H39">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>11.9</v>
+      </c>
+      <c r="K39">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L39">
+        <v>11.8</v>
+      </c>
+      <c r="M39">
+        <v>1.6168445</v>
+      </c>
+      <c r="N39">
+        <v>10.1831555</v>
+      </c>
+      <c r="O39">
+        <v>2.2912099875</v>
+      </c>
+      <c r="P39">
+        <v>7.891945512500001</v>
+      </c>
+      <c r="Q39">
+        <v>7.991945512500001</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.2542556164160558</v>
+      </c>
+      <c r="T39">
+        <v>1.398335791468187</v>
+      </c>
+      <c r="U39">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V39">
+        <v>0.225</v>
+      </c>
+      <c r="W39">
+        <v>0.04107500000000001</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>7.298166273874823</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1750683958973158</v>
+      </c>
+      <c r="C40">
+        <v>59.22747622928137</v>
+      </c>
+      <c r="D40">
+        <v>87.46847622928136</v>
+      </c>
+      <c r="E40">
+        <v>24.48099999999999</v>
+      </c>
+      <c r="F40">
+        <v>31.331</v>
+      </c>
+      <c r="G40">
+        <v>3.09</v>
+      </c>
+      <c r="H40">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>11.9</v>
+      </c>
+      <c r="K40">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L40">
+        <v>11.8</v>
+      </c>
+      <c r="M40">
+        <v>1.660543</v>
+      </c>
+      <c r="N40">
+        <v>10.139457</v>
+      </c>
+      <c r="O40">
+        <v>2.281377825</v>
+      </c>
+      <c r="P40">
+        <v>7.858079175</v>
+      </c>
+      <c r="Q40">
+        <v>7.958079175</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.2571933804795417</v>
+      </c>
+      <c r="T40">
+        <v>1.417402273489842</v>
+      </c>
+      <c r="U40">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V40">
+        <v>0.225</v>
+      </c>
+      <c r="W40">
+        <v>0.04107500000000001</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>7.10610926666759</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1747580034525166</v>
+      </c>
+      <c r="C41">
+        <v>58.60266696826135</v>
+      </c>
+      <c r="D41">
+        <v>87.66816696826135</v>
+      </c>
+      <c r="E41">
+        <v>25.30549999999999</v>
+      </c>
+      <c r="F41">
+        <v>32.1555</v>
+      </c>
+      <c r="G41">
+        <v>3.09</v>
+      </c>
+      <c r="H41">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>11.9</v>
+      </c>
+      <c r="K41">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L41">
+        <v>11.8</v>
+      </c>
+      <c r="M41">
+        <v>1.7042415</v>
+      </c>
+      <c r="N41">
+        <v>10.0957585</v>
+      </c>
+      <c r="O41">
+        <v>2.2715456625</v>
+      </c>
+      <c r="P41">
+        <v>7.824212837500001</v>
+      </c>
+      <c r="Q41">
+        <v>7.924212837500001</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.2602274646762567</v>
+      </c>
+      <c r="T41">
+        <v>1.437093886069584</v>
+      </c>
+      <c r="U41">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V41">
+        <v>0.225</v>
+      </c>
+      <c r="W41">
+        <v>0.04107500000000001</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>6.923901336753037</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1744476110077172</v>
+      </c>
+      <c r="C42">
+        <v>57.97877158248345</v>
+      </c>
+      <c r="D42">
+        <v>87.86877158248345</v>
+      </c>
+      <c r="E42">
+        <v>26.13</v>
+      </c>
+      <c r="F42">
+        <v>32.98</v>
+      </c>
+      <c r="G42">
+        <v>3.09</v>
+      </c>
+      <c r="H42">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>11.9</v>
+      </c>
+      <c r="K42">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L42">
+        <v>11.8</v>
+      </c>
+      <c r="M42">
+        <v>1.74794</v>
+      </c>
+      <c r="N42">
+        <v>10.05206</v>
+      </c>
+      <c r="O42">
+        <v>2.2617135</v>
+      </c>
+      <c r="P42">
+        <v>7.790346500000001</v>
+      </c>
+      <c r="Q42">
+        <v>7.890346500000001</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.2633626850128621</v>
+      </c>
+      <c r="T42">
+        <v>1.457441885735317</v>
+      </c>
+      <c r="U42">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V42">
+        <v>0.225</v>
+      </c>
+      <c r="W42">
+        <v>0.04107500000000001</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>6.750803803334211</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1741372185629179</v>
+      </c>
+      <c r="C43">
+        <v>57.35579635979605</v>
+      </c>
+      <c r="D43">
+        <v>88.07029635979605</v>
+      </c>
+      <c r="E43">
+        <v>26.9545</v>
+      </c>
+      <c r="F43">
+        <v>33.8045</v>
+      </c>
+      <c r="G43">
+        <v>3.09</v>
+      </c>
+      <c r="H43">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>11.9</v>
+      </c>
+      <c r="K43">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L43">
+        <v>11.8</v>
+      </c>
+      <c r="M43">
+        <v>1.7916385</v>
+      </c>
+      <c r="N43">
+        <v>10.0083615</v>
+      </c>
+      <c r="O43">
+        <v>2.2518813375</v>
+      </c>
+      <c r="P43">
+        <v>7.756480162500001</v>
+      </c>
+      <c r="Q43">
+        <v>7.8564801625</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.2666041840049457</v>
+      </c>
+      <c r="T43">
+        <v>1.478479648101584</v>
+      </c>
+      <c r="U43">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V43">
+        <v>0.225</v>
+      </c>
+      <c r="W43">
+        <v>0.04107500000000001</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>6.586150052033377</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1738268261181186</v>
+      </c>
+      <c r="C44">
+        <v>56.73374764586423</v>
+      </c>
+      <c r="D44">
+        <v>88.27274764586421</v>
+      </c>
+      <c r="E44">
+        <v>27.77899999999999</v>
+      </c>
+      <c r="F44">
+        <v>34.62899999999999</v>
+      </c>
+      <c r="G44">
+        <v>3.09</v>
+      </c>
+      <c r="H44">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>11.9</v>
+      </c>
+      <c r="K44">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L44">
+        <v>11.8</v>
+      </c>
+      <c r="M44">
+        <v>1.835337</v>
+      </c>
+      <c r="N44">
+        <v>9.964663000000002</v>
+      </c>
+      <c r="O44">
+        <v>2.242049175</v>
+      </c>
+      <c r="P44">
+        <v>7.722613825000002</v>
+      </c>
+      <c r="Q44">
+        <v>7.822613825000001</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.2699574588243425</v>
+      </c>
+      <c r="T44">
+        <v>1.500242850549447</v>
+      </c>
+      <c r="U44">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V44">
+        <v>0.225</v>
+      </c>
+      <c r="W44">
+        <v>0.04107500000000001</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>6.429336955556392</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1735164336733194</v>
+      </c>
+      <c r="C45">
+        <v>56.11263184483576</v>
+      </c>
+      <c r="D45">
+        <v>88.47613184483575</v>
+      </c>
+      <c r="E45">
+        <v>28.60349999999999</v>
+      </c>
+      <c r="F45">
+        <v>35.45349999999999</v>
+      </c>
+      <c r="G45">
+        <v>3.09</v>
+      </c>
+      <c r="H45">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>11.9</v>
+      </c>
+      <c r="K45">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L45">
+        <v>11.8</v>
+      </c>
+      <c r="M45">
+        <v>1.8790355</v>
+      </c>
+      <c r="N45">
+        <v>9.9209645</v>
+      </c>
+      <c r="O45">
+        <v>2.2322170125</v>
+      </c>
+      <c r="P45">
+        <v>7.688747487500001</v>
+      </c>
+      <c r="Q45">
+        <v>7.7887474875</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.2734283924093322</v>
+      </c>
+      <c r="T45">
+        <v>1.522769674135831</v>
+      </c>
+      <c r="U45">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V45">
+        <v>0.225</v>
+      </c>
+      <c r="W45">
+        <v>0.04107500000000001</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>6.279817491473685</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1738880412285201</v>
+      </c>
+      <c r="C46">
+        <v>55.0447468734536</v>
+      </c>
+      <c r="D46">
+        <v>88.23274687345359</v>
+      </c>
+      <c r="E46">
+        <v>29.428</v>
+      </c>
+      <c r="F46">
+        <v>36.278</v>
+      </c>
+      <c r="G46">
+        <v>3.09</v>
+      </c>
+      <c r="H46">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>11.9</v>
+      </c>
+      <c r="K46">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L46">
+        <v>11.8</v>
+      </c>
+      <c r="M46">
+        <v>1.99529</v>
+      </c>
+      <c r="N46">
+        <v>9.80471</v>
+      </c>
+      <c r="O46">
+        <v>2.20605975</v>
+      </c>
+      <c r="P46">
+        <v>7.59865025</v>
+      </c>
+      <c r="Q46">
+        <v>7.69865025</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.2770232879080715</v>
+      </c>
+      <c r="T46">
+        <v>1.546101027136014</v>
+      </c>
+      <c r="U46">
+        <v>0.055</v>
+      </c>
+      <c r="V46">
+        <v>0.225</v>
+      </c>
+      <c r="W46">
+        <v>0.042625</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>5.913927298788647</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1735931487837208</v>
+      </c>
+      <c r="C47">
+        <v>54.41327723643308</v>
+      </c>
+      <c r="D47">
+        <v>88.42577723643308</v>
+      </c>
+      <c r="E47">
+        <v>30.2525</v>
+      </c>
+      <c r="F47">
+        <v>37.1025</v>
+      </c>
+      <c r="G47">
+        <v>3.09</v>
+      </c>
+      <c r="H47">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>11.9</v>
+      </c>
+      <c r="K47">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L47">
+        <v>11.8</v>
+      </c>
+      <c r="M47">
+        <v>2.0406375</v>
+      </c>
+      <c r="N47">
+        <v>9.759362500000002</v>
+      </c>
+      <c r="O47">
+        <v>2.1958565625</v>
+      </c>
+      <c r="P47">
+        <v>7.563505937500001</v>
+      </c>
+      <c r="Q47">
+        <v>7.663505937500001</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.2807489068794923</v>
+      </c>
+      <c r="T47">
+        <v>1.570280792972567</v>
+      </c>
+      <c r="U47">
+        <v>0.055</v>
+      </c>
+      <c r="V47">
+        <v>0.225</v>
+      </c>
+      <c r="W47">
+        <v>0.042625</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>5.782506692148901</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1732982563389215</v>
+      </c>
+      <c r="C48">
+        <v>53.78265405195716</v>
+      </c>
+      <c r="D48">
+        <v>88.61965405195716</v>
+      </c>
+      <c r="E48">
+        <v>31.077</v>
+      </c>
+      <c r="F48">
+        <v>37.927</v>
+      </c>
+      <c r="G48">
+        <v>3.09</v>
+      </c>
+      <c r="H48">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>11.9</v>
+      </c>
+      <c r="K48">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L48">
+        <v>11.8</v>
+      </c>
+      <c r="M48">
+        <v>2.085985</v>
+      </c>
+      <c r="N48">
+        <v>9.714015</v>
+      </c>
+      <c r="O48">
+        <v>2.185653375</v>
+      </c>
+      <c r="P48">
+        <v>7.528361625000001</v>
+      </c>
+      <c r="Q48">
+        <v>7.628361625</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.2846125117387434</v>
+      </c>
+      <c r="T48">
+        <v>1.595356105691956</v>
+      </c>
+      <c r="U48">
+        <v>0.055</v>
+      </c>
+      <c r="V48">
+        <v>0.225</v>
+      </c>
+      <c r="W48">
+        <v>0.042625</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>5.656800024928271</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1730033638941221</v>
+      </c>
+      <c r="C49">
+        <v>53.15288289989625</v>
+      </c>
+      <c r="D49">
+        <v>88.81438289989624</v>
+      </c>
+      <c r="E49">
+        <v>31.9015</v>
+      </c>
+      <c r="F49">
+        <v>38.7515</v>
+      </c>
+      <c r="G49">
+        <v>3.09</v>
+      </c>
+      <c r="H49">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>11.9</v>
+      </c>
+      <c r="K49">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L49">
+        <v>11.8</v>
+      </c>
+      <c r="M49">
+        <v>2.1313325</v>
+      </c>
+      <c r="N49">
+        <v>9.668667500000002</v>
+      </c>
+      <c r="O49">
+        <v>2.1754501875</v>
+      </c>
+      <c r="P49">
+        <v>7.493217312500001</v>
+      </c>
+      <c r="Q49">
+        <v>7.593217312500001</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.2886219130077776</v>
+      </c>
+      <c r="T49">
+        <v>1.621377656627171</v>
+      </c>
+      <c r="U49">
+        <v>0.055</v>
+      </c>
+      <c r="V49">
+        <v>0.225</v>
+      </c>
+      <c r="W49">
+        <v>0.042625</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>5.536442577589373</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1727084714493229</v>
+      </c>
+      <c r="C50">
+        <v>52.52396940927255</v>
+      </c>
+      <c r="D50">
+        <v>89.00996940927254</v>
+      </c>
+      <c r="E50">
+        <v>32.72599999999999</v>
+      </c>
+      <c r="F50">
+        <v>39.57599999999999</v>
+      </c>
+      <c r="G50">
+        <v>3.09</v>
+      </c>
+      <c r="H50">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>11.9</v>
+      </c>
+      <c r="K50">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L50">
+        <v>11.8</v>
+      </c>
+      <c r="M50">
+        <v>2.17668</v>
+      </c>
+      <c r="N50">
+        <v>9.623320000000001</v>
+      </c>
+      <c r="O50">
+        <v>2.165247</v>
+      </c>
+      <c r="P50">
+        <v>7.458073000000002</v>
+      </c>
+      <c r="Q50">
+        <v>7.558073000000001</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.2927855220179286</v>
+      </c>
+      <c r="T50">
+        <v>1.648400036444509</v>
+      </c>
+      <c r="U50">
+        <v>0.055</v>
+      </c>
+      <c r="V50">
+        <v>0.225</v>
+      </c>
+      <c r="W50">
+        <v>0.042625</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>5.421100023889594</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1724135790045235</v>
+      </c>
+      <c r="C51">
+        <v>51.89591925880264</v>
+      </c>
+      <c r="D51">
+        <v>89.20641925880263</v>
+      </c>
+      <c r="E51">
+        <v>33.55049999999999</v>
+      </c>
+      <c r="F51">
+        <v>40.40049999999999</v>
+      </c>
+      <c r="G51">
+        <v>3.09</v>
+      </c>
+      <c r="H51">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>11.9</v>
+      </c>
+      <c r="K51">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L51">
+        <v>11.8</v>
+      </c>
+      <c r="M51">
+        <v>2.2220275</v>
+      </c>
+      <c r="N51">
+        <v>9.577972500000001</v>
+      </c>
+      <c r="O51">
+        <v>2.1550438125</v>
+      </c>
+      <c r="P51">
+        <v>7.422928687500001</v>
+      </c>
+      <c r="Q51">
+        <v>7.5229286875</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.2971124098127912</v>
+      </c>
+      <c r="T51">
+        <v>1.676482117431155</v>
+      </c>
+      <c r="U51">
+        <v>0.055</v>
+      </c>
+      <c r="V51">
+        <v>0.225</v>
+      </c>
+      <c r="W51">
+        <v>0.042625</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>5.310465329524501</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1721186865597242</v>
+      </c>
+      <c r="C52">
+        <v>51.26873817744676</v>
+      </c>
+      <c r="D52">
+        <v>89.40373817744675</v>
+      </c>
+      <c r="E52">
+        <v>34.37499999999999</v>
+      </c>
+      <c r="F52">
+        <v>41.22499999999999</v>
+      </c>
+      <c r="G52">
+        <v>3.09</v>
+      </c>
+      <c r="H52">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>11.9</v>
+      </c>
+      <c r="K52">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L52">
+        <v>11.8</v>
+      </c>
+      <c r="M52">
+        <v>2.267375</v>
+      </c>
+      <c r="N52">
+        <v>9.532625000000001</v>
+      </c>
+      <c r="O52">
+        <v>2.144840625</v>
+      </c>
+      <c r="P52">
+        <v>7.387784375000001</v>
+      </c>
+      <c r="Q52">
+        <v>7.487784375</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.3016123731194484</v>
+      </c>
+      <c r="T52">
+        <v>1.705687481657267</v>
+      </c>
+      <c r="U52">
+        <v>0.055</v>
+      </c>
+      <c r="V52">
+        <v>0.225</v>
+      </c>
+      <c r="W52">
+        <v>0.042625</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>5.20425602293401</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.171823794114925</v>
+      </c>
+      <c r="C53">
+        <v>50.64243194496601</v>
+      </c>
+      <c r="D53">
+        <v>89.601931944966</v>
+      </c>
+      <c r="E53">
+        <v>35.19949999999999</v>
+      </c>
+      <c r="F53">
+        <v>42.04949999999999</v>
+      </c>
+      <c r="G53">
+        <v>3.09</v>
+      </c>
+      <c r="H53">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>11.9</v>
+      </c>
+      <c r="K53">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L53">
+        <v>11.8</v>
+      </c>
+      <c r="M53">
+        <v>2.3127225</v>
+      </c>
+      <c r="N53">
+        <v>9.487277500000001</v>
+      </c>
+      <c r="O53">
+        <v>2.1346374375</v>
+      </c>
+      <c r="P53">
+        <v>7.352640062500001</v>
+      </c>
+      <c r="Q53">
+        <v>7.4526400625</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.306296008397806</v>
+      </c>
+      <c r="T53">
+        <v>1.736084901566077</v>
+      </c>
+      <c r="U53">
+        <v>0.055</v>
+      </c>
+      <c r="V53">
+        <v>0.225</v>
+      </c>
+      <c r="W53">
+        <v>0.042625</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>5.102211787190207</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1715289016701257</v>
+      </c>
+      <c r="C54">
+        <v>50.01700639248656</v>
+      </c>
+      <c r="D54">
+        <v>89.80100639248656</v>
+      </c>
+      <c r="E54">
+        <v>36.02399999999999</v>
+      </c>
+      <c r="F54">
+        <v>42.874</v>
+      </c>
+      <c r="G54">
+        <v>3.09</v>
+      </c>
+      <c r="H54">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>11.9</v>
+      </c>
+      <c r="K54">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L54">
+        <v>11.8</v>
+      </c>
+      <c r="M54">
+        <v>2.35807</v>
+      </c>
+      <c r="N54">
+        <v>9.441930000000001</v>
+      </c>
+      <c r="O54">
+        <v>2.12443425</v>
+      </c>
+      <c r="P54">
+        <v>7.317495750000001</v>
+      </c>
+      <c r="Q54">
+        <v>7.41749575</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.3111747951460951</v>
+      </c>
+      <c r="T54">
+        <v>1.767748880637755</v>
+      </c>
+      <c r="U54">
+        <v>0.055</v>
+      </c>
+      <c r="V54">
+        <v>0.225</v>
+      </c>
+      <c r="W54">
+        <v>0.042625</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>5.004092329744241</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1712340092253264</v>
+      </c>
+      <c r="C55">
+        <v>49.39246740307155</v>
+      </c>
+      <c r="D55">
+        <v>90.00096740307154</v>
+      </c>
+      <c r="E55">
+        <v>36.84849999999999</v>
+      </c>
+      <c r="F55">
+        <v>43.6985</v>
+      </c>
+      <c r="G55">
+        <v>3.09</v>
+      </c>
+      <c r="H55">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>11.9</v>
+      </c>
+      <c r="K55">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L55">
+        <v>11.8</v>
+      </c>
+      <c r="M55">
+        <v>2.4034175</v>
+      </c>
+      <c r="N55">
+        <v>9.396582500000001</v>
+      </c>
+      <c r="O55">
+        <v>2.1142310625</v>
+      </c>
+      <c r="P55">
+        <v>7.282351437500001</v>
+      </c>
+      <c r="Q55">
+        <v>7.382351437500001</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.3162611898411199</v>
+      </c>
+      <c r="T55">
+        <v>1.800760263074184</v>
+      </c>
+      <c r="U55">
+        <v>0.055</v>
+      </c>
+      <c r="V55">
+        <v>0.225</v>
+      </c>
+      <c r="W55">
+        <v>0.042625</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>4.909675493333972</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.170939116780527</v>
+      </c>
+      <c r="C56">
+        <v>48.7688209123006</v>
+      </c>
+      <c r="D56">
+        <v>90.20182091230059</v>
+      </c>
+      <c r="E56">
+        <v>37.67299999999999</v>
+      </c>
+      <c r="F56">
+        <v>44.523</v>
+      </c>
+      <c r="G56">
+        <v>3.09</v>
+      </c>
+      <c r="H56">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>11.9</v>
+      </c>
+      <c r="K56">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L56">
+        <v>11.8</v>
+      </c>
+      <c r="M56">
+        <v>2.448765</v>
+      </c>
+      <c r="N56">
+        <v>9.351235000000001</v>
+      </c>
+      <c r="O56">
+        <v>2.104027875</v>
+      </c>
+      <c r="P56">
+        <v>7.247207125000001</v>
+      </c>
+      <c r="Q56">
+        <v>7.347207125000001</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.3215687321315805</v>
+      </c>
+      <c r="T56">
+        <v>1.83520692300785</v>
+      </c>
+      <c r="U56">
+        <v>0.055</v>
+      </c>
+      <c r="V56">
+        <v>0.225</v>
+      </c>
+      <c r="W56">
+        <v>0.042625</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>4.81875557679075</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1706442243357277</v>
+      </c>
+      <c r="C57">
+        <v>48.14607290885711</v>
+      </c>
+      <c r="D57">
+        <v>90.4035729088571</v>
+      </c>
+      <c r="E57">
+        <v>38.4975</v>
+      </c>
+      <c r="F57">
+        <v>45.3475</v>
+      </c>
+      <c r="G57">
+        <v>3.09</v>
+      </c>
+      <c r="H57">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>11.9</v>
+      </c>
+      <c r="K57">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L57">
+        <v>11.8</v>
+      </c>
+      <c r="M57">
+        <v>2.4941125</v>
+      </c>
+      <c r="N57">
+        <v>9.305887500000001</v>
+      </c>
+      <c r="O57">
+        <v>2.0938246875</v>
+      </c>
+      <c r="P57">
+        <v>7.212062812500001</v>
+      </c>
+      <c r="Q57">
+        <v>7.312062812500001</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.3271121651905061</v>
+      </c>
+      <c r="T57">
+        <v>1.871184545605234</v>
+      </c>
+      <c r="U57">
+        <v>0.055</v>
+      </c>
+      <c r="V57">
+        <v>0.225</v>
+      </c>
+      <c r="W57">
+        <v>0.042625</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>4.731141839030919</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1703493318909284</v>
+      </c>
+      <c r="C58">
+        <v>47.52422943512353</v>
+      </c>
+      <c r="D58">
+        <v>90.60622943512352</v>
+      </c>
+      <c r="E58">
+        <v>39.322</v>
+      </c>
+      <c r="F58">
+        <v>46.172</v>
+      </c>
+      <c r="G58">
+        <v>3.09</v>
+      </c>
+      <c r="H58">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>11.9</v>
+      </c>
+      <c r="K58">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L58">
+        <v>11.8</v>
+      </c>
+      <c r="M58">
+        <v>2.53946</v>
+      </c>
+      <c r="N58">
+        <v>9.260540000000001</v>
+      </c>
+      <c r="O58">
+        <v>2.0836215</v>
+      </c>
+      <c r="P58">
+        <v>7.176918500000001</v>
+      </c>
+      <c r="Q58">
+        <v>7.276918500000001</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.3329075724793829</v>
+      </c>
+      <c r="T58">
+        <v>1.908797514684317</v>
+      </c>
+      <c r="U58">
+        <v>0.055</v>
+      </c>
+      <c r="V58">
+        <v>0.225</v>
+      </c>
+      <c r="W58">
+        <v>0.042625</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>4.646657163333938</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1700544394461291</v>
+      </c>
+      <c r="C59">
+        <v>46.90329658778458</v>
+      </c>
+      <c r="D59">
+        <v>90.80979658778458</v>
+      </c>
+      <c r="E59">
+        <v>40.1465</v>
+      </c>
+      <c r="F59">
+        <v>46.9965</v>
+      </c>
+      <c r="G59">
+        <v>3.09</v>
+      </c>
+      <c r="H59">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>11.9</v>
+      </c>
+      <c r="K59">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L59">
+        <v>11.8</v>
+      </c>
+      <c r="M59">
+        <v>2.5848075</v>
+      </c>
+      <c r="N59">
+        <v>9.215192500000001</v>
+      </c>
+      <c r="O59">
+        <v>2.0734183125</v>
+      </c>
+      <c r="P59">
+        <v>7.141774187500001</v>
+      </c>
+      <c r="Q59">
+        <v>7.241774187500001</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.3389725335956492</v>
+      </c>
+      <c r="T59">
+        <v>1.948159924185683</v>
+      </c>
+      <c r="U59">
+        <v>0.055</v>
+      </c>
+      <c r="V59">
+        <v>0.225</v>
+      </c>
+      <c r="W59">
+        <v>0.042625</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>4.565136862222817</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1714676470013298</v>
+      </c>
+      <c r="C60">
+        <v>45.11146888186085</v>
+      </c>
+      <c r="D60">
+        <v>89.84246888186084</v>
+      </c>
+      <c r="E60">
+        <v>40.97099999999999</v>
+      </c>
+      <c r="F60">
+        <v>47.82099999999999</v>
+      </c>
+      <c r="G60">
+        <v>3.09</v>
+      </c>
+      <c r="H60">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>11.9</v>
+      </c>
+      <c r="K60">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L60">
+        <v>11.8</v>
+      </c>
+      <c r="M60">
+        <v>2.8118748</v>
+      </c>
+      <c r="N60">
+        <v>8.988125200000001</v>
+      </c>
+      <c r="O60">
+        <v>2.02232817</v>
+      </c>
+      <c r="P60">
+        <v>6.965797030000001</v>
+      </c>
+      <c r="Q60">
+        <v>7.065797030000001</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.3453263023841186</v>
+      </c>
+      <c r="T60">
+        <v>1.989396734139495</v>
+      </c>
+      <c r="U60">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V60">
+        <v>0.225</v>
+      </c>
+      <c r="W60">
+        <v>0.04557000000000001</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>4.196488406951833</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.1712022045565305</v>
+      </c>
+      <c r="C61">
+        <v>44.4670867633318</v>
+      </c>
+      <c r="D61">
+        <v>90.02258676333179</v>
+      </c>
+      <c r="E61">
+        <v>41.79549999999999</v>
+      </c>
+      <c r="F61">
+        <v>48.64549999999999</v>
+      </c>
+      <c r="G61">
+        <v>3.09</v>
+      </c>
+      <c r="H61">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>11.9</v>
+      </c>
+      <c r="K61">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L61">
+        <v>11.8</v>
+      </c>
+      <c r="M61">
+        <v>2.8603554</v>
+      </c>
+      <c r="N61">
+        <v>8.939644600000001</v>
+      </c>
+      <c r="O61">
+        <v>2.011420035</v>
+      </c>
+      <c r="P61">
+        <v>6.928224565000001</v>
+      </c>
+      <c r="Q61">
+        <v>7.028224565</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.3519900111134891</v>
+      </c>
+      <c r="T61">
+        <v>2.032645095798371</v>
+      </c>
+      <c r="U61">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V61">
+        <v>0.225</v>
+      </c>
+      <c r="W61">
+        <v>0.04557000000000001</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>4.125361484800107</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1709367621117312</v>
+      </c>
+      <c r="C62">
+        <v>43.82342830307993</v>
+      </c>
+      <c r="D62">
+        <v>90.20342830307992</v>
+      </c>
+      <c r="E62">
+        <v>42.61999999999999</v>
+      </c>
+      <c r="F62">
+        <v>49.46999999999999</v>
+      </c>
+      <c r="G62">
+        <v>3.09</v>
+      </c>
+      <c r="H62">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>11.9</v>
+      </c>
+      <c r="K62">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L62">
+        <v>11.8</v>
+      </c>
+      <c r="M62">
+        <v>2.908836</v>
+      </c>
+      <c r="N62">
+        <v>8.891164</v>
+      </c>
+      <c r="O62">
+        <v>2.0005119</v>
+      </c>
+      <c r="P62">
+        <v>6.890652100000001</v>
+      </c>
+      <c r="Q62">
+        <v>6.9906521</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.358986905279328</v>
+      </c>
+      <c r="T62">
+        <v>2.078055875540191</v>
+      </c>
+      <c r="U62">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V62">
+        <v>0.225</v>
+      </c>
+      <c r="W62">
+        <v>0.04557000000000001</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>4.056605460053437</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.1726568696669319</v>
+      </c>
+      <c r="C63">
+        <v>41.83978272530563</v>
+      </c>
+      <c r="D63">
+        <v>89.04428272530562</v>
+      </c>
+      <c r="E63">
+        <v>43.44449999999999</v>
+      </c>
+      <c r="F63">
+        <v>50.29449999999999</v>
+      </c>
+      <c r="G63">
+        <v>3.09</v>
+      </c>
+      <c r="H63">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>11.9</v>
+      </c>
+      <c r="K63">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L63">
+        <v>11.8</v>
+      </c>
+      <c r="M63">
+        <v>3.168553499999999</v>
+      </c>
+      <c r="N63">
+        <v>8.631446500000001</v>
+      </c>
+      <c r="O63">
+        <v>1.9420754625</v>
+      </c>
+      <c r="P63">
+        <v>6.689371037500001</v>
+      </c>
+      <c r="Q63">
+        <v>6.7893710375</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.3663426145305947</v>
+      </c>
+      <c r="T63">
+        <v>2.12579541321749</v>
+      </c>
+      <c r="U63">
+        <v>0.063</v>
+      </c>
+      <c r="V63">
+        <v>0.225</v>
+      </c>
+      <c r="W63">
+        <v>0.048825</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>3.724096815786763</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.1724239772221326</v>
+      </c>
+      <c r="C64">
+        <v>41.17047748249225</v>
+      </c>
+      <c r="D64">
+        <v>89.19947748249224</v>
+      </c>
+      <c r="E64">
+        <v>44.26899999999999</v>
+      </c>
+      <c r="F64">
+        <v>51.11899999999999</v>
+      </c>
+      <c r="G64">
+        <v>3.09</v>
+      </c>
+      <c r="H64">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>11.9</v>
+      </c>
+      <c r="K64">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L64">
+        <v>11.8</v>
+      </c>
+      <c r="M64">
+        <v>3.220496999999999</v>
+      </c>
+      <c r="N64">
+        <v>8.579503000000001</v>
+      </c>
+      <c r="O64">
+        <v>1.930388175</v>
+      </c>
+      <c r="P64">
+        <v>6.649114825000001</v>
+      </c>
+      <c r="Q64">
+        <v>6.749114825</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.3740854663740332</v>
+      </c>
+      <c r="T64">
+        <v>2.176047558140961</v>
+      </c>
+      <c r="U64">
+        <v>0.063</v>
+      </c>
+      <c r="V64">
+        <v>0.225</v>
+      </c>
+      <c r="W64">
+        <v>0.048825</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>3.664030738112783</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.1721910847773333</v>
+      </c>
+      <c r="C65">
+        <v>40.50171416024995</v>
+      </c>
+      <c r="D65">
+        <v>89.35521416024994</v>
+      </c>
+      <c r="E65">
+        <v>45.09349999999999</v>
+      </c>
+      <c r="F65">
+        <v>51.94349999999999</v>
+      </c>
+      <c r="G65">
+        <v>3.09</v>
+      </c>
+      <c r="H65">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>11.9</v>
+      </c>
+      <c r="K65">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L65">
+        <v>11.8</v>
+      </c>
+      <c r="M65">
+        <v>3.2724405</v>
+      </c>
+      <c r="N65">
+        <v>8.527559500000001</v>
+      </c>
+      <c r="O65">
+        <v>1.9187008875</v>
+      </c>
+      <c r="P65">
+        <v>6.608858612500001</v>
+      </c>
+      <c r="Q65">
+        <v>6.7088586125</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.3822468507495495</v>
+      </c>
+      <c r="T65">
+        <v>2.229016035222458</v>
+      </c>
+      <c r="U65">
+        <v>0.063</v>
+      </c>
+      <c r="V65">
+        <v>0.225</v>
+      </c>
+      <c r="W65">
+        <v>0.048825</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>3.6058715200475</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.171958192332534</v>
+      </c>
+      <c r="C66">
+        <v>39.83349560202091</v>
+      </c>
+      <c r="D66">
+        <v>89.5114956020209</v>
+      </c>
+      <c r="E66">
+        <v>45.91799999999999</v>
+      </c>
+      <c r="F66">
+        <v>52.76799999999999</v>
+      </c>
+      <c r="G66">
+        <v>3.09</v>
+      </c>
+      <c r="H66">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>11.9</v>
+      </c>
+      <c r="K66">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L66">
+        <v>11.8</v>
+      </c>
+      <c r="M66">
+        <v>3.324384</v>
+      </c>
+      <c r="N66">
+        <v>8.475616</v>
+      </c>
+      <c r="O66">
+        <v>1.9070136</v>
+      </c>
+      <c r="P66">
+        <v>6.568602400000001</v>
+      </c>
+      <c r="Q66">
+        <v>6.6686024</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.3908616453681501</v>
+      </c>
+      <c r="T66">
+        <v>2.28492720547515</v>
+      </c>
+      <c r="U66">
+        <v>0.063</v>
+      </c>
+      <c r="V66">
+        <v>0.225</v>
+      </c>
+      <c r="W66">
+        <v>0.048825</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>3.549529777546758</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.1753019248877347</v>
+      </c>
+      <c r="C67">
+        <v>36.81633420068652</v>
+      </c>
+      <c r="D67">
+        <v>87.31883420068651</v>
+      </c>
+      <c r="E67">
+        <v>46.74249999999999</v>
+      </c>
+      <c r="F67">
+        <v>53.59249999999999</v>
+      </c>
+      <c r="G67">
+        <v>3.09</v>
+      </c>
+      <c r="H67">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>11.9</v>
+      </c>
+      <c r="K67">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L67">
+        <v>11.8</v>
+      </c>
+      <c r="M67">
+        <v>3.756834249999999</v>
+      </c>
+      <c r="N67">
+        <v>8.043165750000002</v>
+      </c>
+      <c r="O67">
+        <v>1.80971229375</v>
+      </c>
+      <c r="P67">
+        <v>6.233453456250001</v>
+      </c>
+      <c r="Q67">
+        <v>6.333453456250001</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.3999687139649564</v>
+      </c>
+      <c r="T67">
+        <v>2.344033299742281</v>
+      </c>
+      <c r="U67">
+        <v>0.0701</v>
+      </c>
+      <c r="V67">
+        <v>0.225</v>
+      </c>
+      <c r="W67">
+        <v>0.0543275</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>3.140942403833761</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.1751240574429354</v>
+      </c>
+      <c r="C68">
+        <v>36.10576257263683</v>
+      </c>
+      <c r="D68">
+        <v>87.43276257263682</v>
+      </c>
+      <c r="E68">
+        <v>47.56699999999999</v>
+      </c>
+      <c r="F68">
+        <v>54.41699999999999</v>
+      </c>
+      <c r="G68">
+        <v>3.09</v>
+      </c>
+      <c r="H68">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>11.9</v>
+      </c>
+      <c r="K68">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L68">
+        <v>11.8</v>
+      </c>
+      <c r="M68">
+        <v>3.814631699999999</v>
+      </c>
+      <c r="N68">
+        <v>7.985368300000001</v>
+      </c>
+      <c r="O68">
+        <v>1.7967078675</v>
+      </c>
+      <c r="P68">
+        <v>6.188660432500001</v>
+      </c>
+      <c r="Q68">
+        <v>6.2886604325</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.4096114924792219</v>
+      </c>
+      <c r="T68">
+        <v>2.406616223083949</v>
+      </c>
+      <c r="U68">
+        <v>0.0701</v>
+      </c>
+      <c r="V68">
+        <v>0.225</v>
+      </c>
+      <c r="W68">
+        <v>0.0543275</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>3.093352367412037</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.1749461899981361</v>
+      </c>
+      <c r="C69">
+        <v>35.3954886267831</v>
+      </c>
+      <c r="D69">
+        <v>87.54698862678309</v>
+      </c>
+      <c r="E69">
+        <v>48.39149999999999</v>
+      </c>
+      <c r="F69">
+        <v>55.24149999999999</v>
+      </c>
+      <c r="G69">
+        <v>3.09</v>
+      </c>
+      <c r="H69">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>11.9</v>
+      </c>
+      <c r="K69">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L69">
+        <v>11.8</v>
+      </c>
+      <c r="M69">
+        <v>3.872429149999999</v>
+      </c>
+      <c r="N69">
+        <v>7.927570850000001</v>
+      </c>
+      <c r="O69">
+        <v>1.78370344125</v>
+      </c>
+      <c r="P69">
+        <v>6.143867408750001</v>
+      </c>
+      <c r="Q69">
+        <v>6.243867408750001</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.4198386818125338</v>
+      </c>
+      <c r="T69">
+        <v>2.472992050870567</v>
+      </c>
+      <c r="U69">
+        <v>0.0701</v>
+      </c>
+      <c r="V69">
+        <v>0.225</v>
+      </c>
+      <c r="W69">
+        <v>0.0543275</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>3.047182929092454</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.1747683225533368</v>
+      </c>
+      <c r="C70">
+        <v>34.68551353136748</v>
+      </c>
+      <c r="D70">
+        <v>87.66151353136748</v>
+      </c>
+      <c r="E70">
+        <v>49.21599999999999</v>
+      </c>
+      <c r="F70">
+        <v>56.066</v>
+      </c>
+      <c r="G70">
+        <v>3.09</v>
+      </c>
+      <c r="H70">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>11.9</v>
+      </c>
+      <c r="K70">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L70">
+        <v>11.8</v>
+      </c>
+      <c r="M70">
+        <v>3.930226599999999</v>
+      </c>
+      <c r="N70">
+        <v>7.869773400000001</v>
+      </c>
+      <c r="O70">
+        <v>1.770699015</v>
+      </c>
+      <c r="P70">
+        <v>6.099074385000002</v>
+      </c>
+      <c r="Q70">
+        <v>6.199074385000001</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.4307050704791777</v>
+      </c>
+      <c r="T70">
+        <v>2.543516367893848</v>
+      </c>
+      <c r="U70">
+        <v>0.0701</v>
+      </c>
+      <c r="V70">
+        <v>0.225</v>
+      </c>
+      <c r="W70">
+        <v>0.0543275</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>3.00237141542933</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.1859806301085375</v>
+      </c>
+      <c r="C71">
+        <v>27.18290752147166</v>
+      </c>
+      <c r="D71">
+        <v>80.98340752147165</v>
+      </c>
+      <c r="E71">
+        <v>50.04049999999999</v>
+      </c>
+      <c r="F71">
+        <v>56.8905</v>
+      </c>
+      <c r="G71">
+        <v>3.09</v>
+      </c>
+      <c r="H71">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>11.9</v>
+      </c>
+      <c r="K71">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L71">
+        <v>11.8</v>
+      </c>
+      <c r="M71">
+        <v>5.1997917</v>
+      </c>
+      <c r="N71">
+        <v>6.6002083</v>
+      </c>
+      <c r="O71">
+        <v>1.4850468675</v>
+      </c>
+      <c r="P71">
+        <v>5.115161432500001</v>
+      </c>
+      <c r="Q71">
+        <v>5.2151614325</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.4422725164791534</v>
+      </c>
+      <c r="T71">
+        <v>2.618590640854115</v>
+      </c>
+      <c r="U71">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V71">
+        <v>0.225</v>
+      </c>
+      <c r="W71">
+        <v>0.07083500000000001</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>2.269321673020094</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.1859678376637382</v>
+      </c>
+      <c r="C72">
+        <v>26.36544693841781</v>
+      </c>
+      <c r="D72">
+        <v>80.9904469384178</v>
+      </c>
+      <c r="E72">
+        <v>50.86499999999999</v>
+      </c>
+      <c r="F72">
+        <v>57.715</v>
+      </c>
+      <c r="G72">
+        <v>3.09</v>
+      </c>
+      <c r="H72">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>11.9</v>
+      </c>
+      <c r="K72">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L72">
+        <v>11.8</v>
+      </c>
+      <c r="M72">
+        <v>5.275151</v>
+      </c>
+      <c r="N72">
+        <v>6.524849000000001</v>
+      </c>
+      <c r="O72">
+        <v>1.468091025</v>
+      </c>
+      <c r="P72">
+        <v>5.056757975000001</v>
+      </c>
+      <c r="Q72">
+        <v>5.156757975000001</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.4546111255457941</v>
+      </c>
+      <c r="T72">
+        <v>2.698669865345066</v>
+      </c>
+      <c r="U72">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V72">
+        <v>0.225</v>
+      </c>
+      <c r="W72">
+        <v>0.07083500000000001</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>2.23690279197695</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.1859550452189389</v>
+      </c>
+      <c r="C73">
+        <v>25.54798757926156</v>
+      </c>
+      <c r="D73">
+        <v>80.99748757926154</v>
+      </c>
+      <c r="E73">
+        <v>51.68949999999999</v>
+      </c>
+      <c r="F73">
+        <v>58.53949999999999</v>
+      </c>
+      <c r="G73">
+        <v>3.09</v>
+      </c>
+      <c r="H73">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>11.9</v>
+      </c>
+      <c r="K73">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L73">
+        <v>11.8</v>
+      </c>
+      <c r="M73">
+        <v>5.3505103</v>
+      </c>
+      <c r="N73">
+        <v>6.449489700000001</v>
+      </c>
+      <c r="O73">
+        <v>1.4511351825</v>
+      </c>
+      <c r="P73">
+        <v>4.998354517500001</v>
+      </c>
+      <c r="Q73">
+        <v>5.098354517500001</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.4678006731687548</v>
+      </c>
+      <c r="T73">
+        <v>2.784271794973324</v>
+      </c>
+      <c r="U73">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V73">
+        <v>0.225</v>
+      </c>
+      <c r="W73">
+        <v>0.07083500000000001</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>2.205397118850514</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.1859422527741396</v>
+      </c>
+      <c r="C74">
+        <v>24.7305294443221</v>
+      </c>
+      <c r="D74">
+        <v>81.00452944432209</v>
+      </c>
+      <c r="E74">
+        <v>52.51399999999999</v>
+      </c>
+      <c r="F74">
+        <v>59.36399999999999</v>
+      </c>
+      <c r="G74">
+        <v>3.09</v>
+      </c>
+      <c r="H74">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>11.9</v>
+      </c>
+      <c r="K74">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L74">
+        <v>11.8</v>
+      </c>
+      <c r="M74">
+        <v>5.4258696</v>
+      </c>
+      <c r="N74">
+        <v>6.374130400000001</v>
+      </c>
+      <c r="O74">
+        <v>1.43417934</v>
+      </c>
+      <c r="P74">
+        <v>4.939951060000001</v>
+      </c>
+      <c r="Q74">
+        <v>5.039951060000001</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.4819323313362129</v>
+      </c>
+      <c r="T74">
+        <v>2.875988148146458</v>
+      </c>
+      <c r="U74">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V74">
+        <v>0.225</v>
+      </c>
+      <c r="W74">
+        <v>0.07083500000000001</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>2.174766603310924</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.1859294603293403</v>
+      </c>
+      <c r="C75">
+        <v>23.91307253391875</v>
+      </c>
+      <c r="D75">
+        <v>81.01157253391874</v>
+      </c>
+      <c r="E75">
+        <v>53.33849999999999</v>
+      </c>
+      <c r="F75">
+        <v>60.18849999999999</v>
+      </c>
+      <c r="G75">
+        <v>3.09</v>
+      </c>
+      <c r="H75">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>11.9</v>
+      </c>
+      <c r="K75">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L75">
+        <v>11.8</v>
+      </c>
+      <c r="M75">
+        <v>5.5012289</v>
+      </c>
+      <c r="N75">
+        <v>6.298771100000001</v>
+      </c>
+      <c r="O75">
+        <v>1.4172234975</v>
+      </c>
+      <c r="P75">
+        <v>4.8815476025</v>
+      </c>
+      <c r="Q75">
+        <v>4.9815476025</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.4971107789975567</v>
+      </c>
+      <c r="T75">
+        <v>2.974498305258343</v>
+      </c>
+      <c r="U75">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V75">
+        <v>0.225</v>
+      </c>
+      <c r="W75">
+        <v>0.07083500000000001</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>2.144975279977897</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.185916667884541</v>
+      </c>
+      <c r="C76">
+        <v>23.09561684837099</v>
+      </c>
+      <c r="D76">
+        <v>81.01861684837098</v>
+      </c>
+      <c r="E76">
+        <v>54.16299999999999</v>
+      </c>
+      <c r="F76">
+        <v>61.01299999999999</v>
+      </c>
+      <c r="G76">
+        <v>3.09</v>
+      </c>
+      <c r="H76">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>11.9</v>
+      </c>
+      <c r="K76">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L76">
+        <v>11.8</v>
+      </c>
+      <c r="M76">
+        <v>5.5765882</v>
+      </c>
+      <c r="N76">
+        <v>6.223411800000001</v>
+      </c>
+      <c r="O76">
+        <v>1.400267655</v>
+      </c>
+      <c r="P76">
+        <v>4.823144145000001</v>
+      </c>
+      <c r="Q76">
+        <v>4.923144145</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.5134567995559269</v>
+      </c>
+      <c r="T76">
+        <v>3.08058616676345</v>
+      </c>
+      <c r="U76">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V76">
+        <v>0.225</v>
+      </c>
+      <c r="W76">
+        <v>0.07083500000000001</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>2.115989127545764</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.1859038754397417</v>
+      </c>
+      <c r="C77">
+        <v>22.27816238799834</v>
+      </c>
+      <c r="D77">
+        <v>81.02566238799832</v>
+      </c>
+      <c r="E77">
+        <v>54.98749999999999</v>
+      </c>
+      <c r="F77">
+        <v>61.83749999999999</v>
+      </c>
+      <c r="G77">
+        <v>3.09</v>
+      </c>
+      <c r="H77">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>11.9</v>
+      </c>
+      <c r="K77">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L77">
+        <v>11.8</v>
+      </c>
+      <c r="M77">
+        <v>5.651947499999999</v>
+      </c>
+      <c r="N77">
+        <v>6.148052500000001</v>
+      </c>
+      <c r="O77">
+        <v>1.3833118125</v>
+      </c>
+      <c r="P77">
+        <v>4.764740687500002</v>
+      </c>
+      <c r="Q77">
+        <v>4.864740687500001</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.5311105017589669</v>
+      </c>
+      <c r="T77">
+        <v>3.195161057188965</v>
+      </c>
+      <c r="U77">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V77">
+        <v>0.225</v>
+      </c>
+      <c r="W77">
+        <v>0.07083500000000001</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>2.087775939178487</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.1858910829949424</v>
+      </c>
+      <c r="C78">
+        <v>21.46070915312046</v>
+      </c>
+      <c r="D78">
+        <v>81.03270915312045</v>
+      </c>
+      <c r="E78">
+        <v>55.81199999999999</v>
+      </c>
+      <c r="F78">
+        <v>62.66199999999999</v>
+      </c>
+      <c r="G78">
+        <v>3.09</v>
+      </c>
+      <c r="H78">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>11.9</v>
+      </c>
+      <c r="K78">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L78">
+        <v>11.8</v>
+      </c>
+      <c r="M78">
+        <v>5.7273068</v>
+      </c>
+      <c r="N78">
+        <v>6.072693200000001</v>
+      </c>
+      <c r="O78">
+        <v>1.36635597</v>
+      </c>
+      <c r="P78">
+        <v>4.706337230000001</v>
+      </c>
+      <c r="Q78">
+        <v>4.80633723</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.5502353458122602</v>
+      </c>
+      <c r="T78">
+        <v>3.31928385514994</v>
+      </c>
+      <c r="U78">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V78">
+        <v>0.225</v>
+      </c>
+      <c r="W78">
+        <v>0.07083500000000001</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>2.060305203136664</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.1858782905501431</v>
+      </c>
+      <c r="C79">
+        <v>20.64325714405715</v>
+      </c>
+      <c r="D79">
+        <v>81.03975714405713</v>
+      </c>
+      <c r="E79">
+        <v>56.63649999999999</v>
+      </c>
+      <c r="F79">
+        <v>63.48649999999999</v>
+      </c>
+      <c r="G79">
+        <v>3.09</v>
+      </c>
+      <c r="H79">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>11.9</v>
+      </c>
+      <c r="K79">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L79">
+        <v>11.8</v>
+      </c>
+      <c r="M79">
+        <v>5.8026661</v>
+      </c>
+      <c r="N79">
+        <v>5.997333900000001</v>
+      </c>
+      <c r="O79">
+        <v>1.3494001275</v>
+      </c>
+      <c r="P79">
+        <v>4.647933772500001</v>
+      </c>
+      <c r="Q79">
+        <v>4.747933772500001</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.571023219783231</v>
+      </c>
+      <c r="T79">
+        <v>3.45419993989013</v>
+      </c>
+      <c r="U79">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V79">
+        <v>0.225</v>
+      </c>
+      <c r="W79">
+        <v>0.07083500000000001</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>2.033547992706318</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.1858654981053438</v>
+      </c>
+      <c r="C80">
+        <v>19.82580636112824</v>
+      </c>
+      <c r="D80">
+        <v>81.04680636112823</v>
+      </c>
+      <c r="E80">
+        <v>57.46099999999999</v>
+      </c>
+      <c r="F80">
+        <v>64.31099999999999</v>
+      </c>
+      <c r="G80">
+        <v>3.09</v>
+      </c>
+      <c r="H80">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>11.9</v>
+      </c>
+      <c r="K80">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L80">
+        <v>11.8</v>
+      </c>
+      <c r="M80">
+        <v>5.8780254</v>
+      </c>
+      <c r="N80">
+        <v>5.9219746</v>
+      </c>
+      <c r="O80">
+        <v>1.332444285</v>
+      </c>
+      <c r="P80">
+        <v>4.589530315</v>
+      </c>
+      <c r="Q80">
+        <v>4.689530315</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.5937009004788356</v>
+      </c>
+      <c r="T80">
+        <v>3.601381123243065</v>
+      </c>
+      <c r="U80">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V80">
+        <v>0.225</v>
+      </c>
+      <c r="W80">
+        <v>0.07083500000000001</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>2.007476864594699</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.1987711806605445</v>
+      </c>
+      <c r="C81">
+        <v>12.46285143011757</v>
+      </c>
+      <c r="D81">
+        <v>74.50835143011756</v>
+      </c>
+      <c r="E81">
+        <v>58.28549999999999</v>
+      </c>
+      <c r="F81">
+        <v>65.13549999999999</v>
+      </c>
+      <c r="G81">
+        <v>3.09</v>
+      </c>
+      <c r="H81">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>11.9</v>
+      </c>
+      <c r="K81">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L81">
+        <v>11.8</v>
+      </c>
+      <c r="M81">
+        <v>7.32774375</v>
+      </c>
+      <c r="N81">
+        <v>4.472256250000001</v>
+      </c>
+      <c r="O81">
+        <v>1.00625765625</v>
+      </c>
+      <c r="P81">
+        <v>3.465998593750001</v>
+      </c>
+      <c r="Q81">
+        <v>3.565998593750001</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.6185383602883072</v>
+      </c>
+      <c r="T81">
+        <v>3.762579562153422</v>
+      </c>
+      <c r="U81">
+        <v>0.1125</v>
+      </c>
+      <c r="V81">
+        <v>0.225</v>
+      </c>
+      <c r="W81">
+        <v>0.0871875</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>1.610318319332605</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.1989219132157452</v>
+      </c>
+      <c r="C82">
+        <v>11.56821215954987</v>
+      </c>
+      <c r="D82">
+        <v>74.43821215954986</v>
+      </c>
+      <c r="E82">
+        <v>59.10999999999999</v>
+      </c>
+      <c r="F82">
+        <v>65.95999999999999</v>
+      </c>
+      <c r="G82">
+        <v>3.09</v>
+      </c>
+      <c r="H82">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>11.9</v>
+      </c>
+      <c r="K82">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L82">
+        <v>11.8</v>
+      </c>
+      <c r="M82">
+        <v>7.4205</v>
+      </c>
+      <c r="N82">
+        <v>4.379500000000001</v>
+      </c>
+      <c r="O82">
+        <v>0.9853875000000002</v>
+      </c>
+      <c r="P82">
+        <v>3.394112500000001</v>
+      </c>
+      <c r="Q82">
+        <v>3.4941125</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.6458595660787263</v>
+      </c>
+      <c r="T82">
+        <v>3.939897844954816</v>
+      </c>
+      <c r="U82">
+        <v>0.1125</v>
+      </c>
+      <c r="V82">
+        <v>0.225</v>
+      </c>
+      <c r="W82">
+        <v>0.0871875</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>1.590189340340947</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.1990726457709459</v>
+      </c>
+      <c r="C83">
+        <v>10.67370481756456</v>
+      </c>
+      <c r="D83">
+        <v>74.36820481756455</v>
+      </c>
+      <c r="E83">
+        <v>59.93449999999999</v>
+      </c>
+      <c r="F83">
+        <v>66.78449999999999</v>
+      </c>
+      <c r="G83">
+        <v>3.09</v>
+      </c>
+      <c r="H83">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>11.9</v>
+      </c>
+      <c r="K83">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L83">
+        <v>11.8</v>
+      </c>
+      <c r="M83">
+        <v>7.51325625</v>
+      </c>
+      <c r="N83">
+        <v>4.286743750000001</v>
+      </c>
+      <c r="O83">
+        <v>0.9645173437500002</v>
+      </c>
+      <c r="P83">
+        <v>3.322226406250001</v>
+      </c>
+      <c r="Q83">
+        <v>3.422226406250001</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.6760566882681365</v>
+      </c>
+      <c r="T83">
+        <v>4.135881210156354</v>
+      </c>
+      <c r="U83">
+        <v>0.1125</v>
+      </c>
+      <c r="V83">
+        <v>0.225</v>
+      </c>
+      <c r="W83">
+        <v>0.0871875</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>1.570557373176245</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.1992233783261466</v>
+      </c>
+      <c r="C84">
+        <v>9.779329032284352</v>
+      </c>
+      <c r="D84">
+        <v>74.29832903228434</v>
+      </c>
+      <c r="E84">
+        <v>60.75899999999999</v>
+      </c>
+      <c r="F84">
+        <v>67.60899999999999</v>
+      </c>
+      <c r="G84">
+        <v>3.09</v>
+      </c>
+      <c r="H84">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>11.9</v>
+      </c>
+      <c r="K84">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L84">
+        <v>11.8</v>
+      </c>
+      <c r="M84">
+        <v>7.606012499999999</v>
+      </c>
+      <c r="N84">
+        <v>4.193987500000001</v>
+      </c>
+      <c r="O84">
+        <v>0.9436471875000002</v>
+      </c>
+      <c r="P84">
+        <v>3.250340312500001</v>
+      </c>
+      <c r="Q84">
+        <v>3.350340312500001</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.7096090462563702</v>
+      </c>
+      <c r="T84">
+        <v>4.353640504824732</v>
+      </c>
+      <c r="U84">
+        <v>0.1125</v>
+      </c>
+      <c r="V84">
+        <v>0.225</v>
+      </c>
+      <c r="W84">
+        <v>0.0871875</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>1.551404234478973</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.1993741108813473</v>
+      </c>
+      <c r="C85">
+        <v>8.885084433228471</v>
+      </c>
+      <c r="D85">
+        <v>74.22858443322846</v>
+      </c>
+      <c r="E85">
+        <v>61.58349999999999</v>
+      </c>
+      <c r="F85">
+        <v>68.4335</v>
+      </c>
+      <c r="G85">
+        <v>3.09</v>
+      </c>
+      <c r="H85">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>11.9</v>
+      </c>
+      <c r="K85">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L85">
+        <v>11.8</v>
+      </c>
+      <c r="M85">
+        <v>7.698768749999999</v>
+      </c>
+      <c r="N85">
+        <v>4.101231250000001</v>
+      </c>
+      <c r="O85">
+        <v>0.9227770312500002</v>
+      </c>
+      <c r="P85">
+        <v>3.178454218750001</v>
+      </c>
+      <c r="Q85">
+        <v>3.278454218750001</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.7471087404785137</v>
+      </c>
+      <c r="T85">
+        <v>4.597018540042329</v>
+      </c>
+      <c r="U85">
+        <v>0.1125</v>
+      </c>
+      <c r="V85">
+        <v>0.225</v>
+      </c>
+      <c r="W85">
+        <v>0.0871875</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>1.532712617196094</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.199524843436548</v>
+      </c>
+      <c r="C86">
+        <v>7.990970651305759</v>
+      </c>
+      <c r="D86">
+        <v>74.15897065130574</v>
+      </c>
+      <c r="E86">
+        <v>62.40799999999998</v>
+      </c>
+      <c r="F86">
+        <v>69.25799999999998</v>
+      </c>
+      <c r="G86">
+        <v>3.09</v>
+      </c>
+      <c r="H86">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>11.9</v>
+      </c>
+      <c r="K86">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L86">
+        <v>11.8</v>
+      </c>
+      <c r="M86">
+        <v>7.791524999999998</v>
+      </c>
+      <c r="N86">
+        <v>4.008475000000002</v>
+      </c>
+      <c r="O86">
+        <v>0.9019068750000004</v>
+      </c>
+      <c r="P86">
+        <v>3.106568125000002</v>
+      </c>
+      <c r="Q86">
+        <v>3.206568125000002</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.7892958964784249</v>
+      </c>
+      <c r="T86">
+        <v>4.870818829662125</v>
+      </c>
+      <c r="U86">
+        <v>0.1125</v>
+      </c>
+      <c r="V86">
+        <v>0.225</v>
+      </c>
+      <c r="W86">
+        <v>0.0871875</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>1.51446603841995</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2645405195163062</v>
+      </c>
+      <c r="C87">
+        <v>-14.19210345229159</v>
+      </c>
+      <c r="D87">
+        <v>52.80039654770839</v>
+      </c>
+      <c r="E87">
+        <v>63.23249999999998</v>
+      </c>
+      <c r="F87">
+        <v>70.08249999999998</v>
+      </c>
+      <c r="G87">
+        <v>3.09</v>
+      </c>
+      <c r="H87">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>11.9</v>
+      </c>
+      <c r="K87">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L87">
+        <v>11.8</v>
+      </c>
+      <c r="M87">
+        <v>13.7782195</v>
+      </c>
+      <c r="N87">
+        <v>-1.978219499999996</v>
+      </c>
+      <c r="O87">
+        <v>-0.4450993874999991</v>
+      </c>
+      <c r="P87">
+        <v>-1.533120112499997</v>
+      </c>
+      <c r="Q87">
+        <v>-1.433120112499997</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.8642123577214029</v>
+      </c>
+      <c r="T87">
+        <v>5.357036691460174</v>
+      </c>
+      <c r="U87">
+        <v>0.1966</v>
+      </c>
+      <c r="V87">
+        <v>0.1926954349943402</v>
+      </c>
+      <c r="W87">
+        <v>0.1587160774801127</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.856424155530401</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2661185195163063</v>
+      </c>
+      <c r="C88">
+        <v>-15.38313331501274</v>
+      </c>
+      <c r="D88">
+        <v>52.43386668498724</v>
+      </c>
+      <c r="E88">
+        <v>64.05699999999999</v>
+      </c>
+      <c r="F88">
+        <v>70.90699999999998</v>
+      </c>
+      <c r="G88">
+        <v>3.09</v>
+      </c>
+      <c r="H88">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>11.9</v>
+      </c>
+      <c r="K88">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L88">
+        <v>11.8</v>
+      </c>
+      <c r="M88">
+        <v>13.9403162</v>
+      </c>
+      <c r="N88">
+        <v>-2.140316199999996</v>
+      </c>
+      <c r="O88">
+        <v>-0.481571144999999</v>
+      </c>
+      <c r="P88">
+        <v>-1.658745054999997</v>
+      </c>
+      <c r="Q88">
+        <v>-1.558745054999997</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.9231703832729319</v>
+      </c>
+      <c r="T88">
+        <v>5.739682169421616</v>
+      </c>
+      <c r="U88">
+        <v>0.1966</v>
+      </c>
+      <c r="V88">
+        <v>0.1904547904013827</v>
+      </c>
+      <c r="W88">
+        <v>0.1591565882070882</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.8464657351172569</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2676965195163062</v>
+      </c>
+      <c r="C89">
+        <v>-16.56910950435694</v>
+      </c>
+      <c r="D89">
+        <v>52.07239049564303</v>
+      </c>
+      <c r="E89">
+        <v>64.88149999999999</v>
+      </c>
+      <c r="F89">
+        <v>71.73149999999998</v>
+      </c>
+      <c r="G89">
+        <v>3.09</v>
+      </c>
+      <c r="H89">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>11.9</v>
+      </c>
+      <c r="K89">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L89">
+        <v>11.8</v>
+      </c>
+      <c r="M89">
+        <v>14.1024129</v>
+      </c>
+      <c r="N89">
+        <v>-2.302412899999995</v>
+      </c>
+      <c r="O89">
+        <v>-0.5180429024999988</v>
+      </c>
+      <c r="P89">
+        <v>-1.784369997499996</v>
+      </c>
+      <c r="Q89">
+        <v>-1.684369997499996</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.9911988742939264</v>
+      </c>
+      <c r="T89">
+        <v>6.181196182454046</v>
+      </c>
+      <c r="U89">
+        <v>0.1966</v>
+      </c>
+      <c r="V89">
+        <v>0.1882656548795278</v>
+      </c>
+      <c r="W89">
+        <v>0.1595869722506848</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.8367362439090125</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2692745195163062</v>
+      </c>
+      <c r="C90">
+        <v>-17.75013582394567</v>
+      </c>
+      <c r="D90">
+        <v>51.71586417605433</v>
+      </c>
+      <c r="E90">
+        <v>65.706</v>
+      </c>
+      <c r="F90">
+        <v>72.556</v>
+      </c>
+      <c r="G90">
+        <v>3.09</v>
+      </c>
+      <c r="H90">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>11.9</v>
+      </c>
+      <c r="K90">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L90">
+        <v>11.8</v>
+      </c>
+      <c r="M90">
+        <v>14.2645096</v>
+      </c>
+      <c r="N90">
+        <v>-2.464509599999998</v>
+      </c>
+      <c r="O90">
+        <v>-0.5545146599999995</v>
+      </c>
+      <c r="P90">
+        <v>-1.909994939999998</v>
+      </c>
+      <c r="Q90">
+        <v>-1.809994939999999</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>1.070565447151754</v>
+      </c>
+      <c r="T90">
+        <v>6.696295864325219</v>
+      </c>
+      <c r="U90">
+        <v>0.1966</v>
+      </c>
+      <c r="V90">
+        <v>0.186126272437715</v>
+      </c>
+      <c r="W90">
+        <v>0.1600075748387452</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.8272278775009554</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2708525195163063</v>
+      </c>
+      <c r="C91">
+        <v>-18.92631325386509</v>
+      </c>
+      <c r="D91">
+        <v>51.36418674613491</v>
+      </c>
+      <c r="E91">
+        <v>66.5305</v>
+      </c>
+      <c r="F91">
+        <v>73.3805</v>
+      </c>
+      <c r="G91">
+        <v>3.09</v>
+      </c>
+      <c r="H91">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>11.9</v>
+      </c>
+      <c r="K91">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L91">
+        <v>11.8</v>
+      </c>
+      <c r="M91">
+        <v>14.4266063</v>
+      </c>
+      <c r="N91">
+        <v>-2.626606299999999</v>
+      </c>
+      <c r="O91">
+        <v>-0.5909864174999997</v>
+      </c>
+      <c r="P91">
+        <v>-2.035619882499999</v>
+      </c>
+      <c r="Q91">
+        <v>-1.935619882499999</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>1.164362305983732</v>
+      </c>
+      <c r="T91">
+        <v>7.30505003380933</v>
+      </c>
+      <c r="U91">
+        <v>0.1966</v>
+      </c>
+      <c r="V91">
+        <v>0.1840349660058305</v>
+      </c>
+      <c r="W91">
+        <v>0.1604187256832537</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.8179331822481356</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2724305195163063</v>
+      </c>
+      <c r="C92">
+        <v>-20.09774004602052</v>
+      </c>
+      <c r="D92">
+        <v>51.01725995397948</v>
+      </c>
+      <c r="E92">
+        <v>67.355</v>
+      </c>
+      <c r="F92">
+        <v>74.205</v>
+      </c>
+      <c r="G92">
+        <v>3.09</v>
+      </c>
+      <c r="H92">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>11.9</v>
+      </c>
+      <c r="K92">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L92">
+        <v>11.8</v>
+      </c>
+      <c r="M92">
+        <v>14.588703</v>
+      </c>
+      <c r="N92">
+        <v>-2.788702999999998</v>
+      </c>
+      <c r="O92">
+        <v>-0.6274581749999996</v>
+      </c>
+      <c r="P92">
+        <v>-2.161244824999998</v>
+      </c>
+      <c r="Q92">
+        <v>-2.061244824999999</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>1.276918536582105</v>
+      </c>
+      <c r="T92">
+        <v>8.035555037190264</v>
+      </c>
+      <c r="U92">
+        <v>0.1966</v>
+      </c>
+      <c r="V92">
+        <v>0.1819901330502102</v>
+      </c>
+      <c r="W92">
+        <v>0.1608207398423287</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.8088450357787119</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2916115252620192</v>
+      </c>
+      <c r="C93">
+        <v>-24.79295897504723</v>
+      </c>
+      <c r="D93">
+        <v>47.14654102495277</v>
+      </c>
+      <c r="E93">
+        <v>68.1795</v>
+      </c>
+      <c r="F93">
+        <v>75.0295</v>
+      </c>
+      <c r="G93">
+        <v>3.09</v>
+      </c>
+      <c r="H93">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>11.9</v>
+      </c>
+      <c r="K93">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L93">
+        <v>11.8</v>
+      </c>
+      <c r="M93">
+        <v>16.0413071</v>
+      </c>
+      <c r="N93">
+        <v>-4.241307099999997</v>
+      </c>
+      <c r="O93">
+        <v>-0.9542940974999992</v>
+      </c>
+      <c r="P93">
+        <v>-3.287013002499998</v>
+      </c>
+      <c r="Q93">
+        <v>-3.187013002499998</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>1.436165104488039</v>
+      </c>
+      <c r="T93">
+        <v>9.069086579674305</v>
+      </c>
+      <c r="U93">
+        <v>0.2138</v>
+      </c>
+      <c r="V93">
+        <v>0.1655102033424695</v>
+      </c>
+      <c r="W93">
+        <v>0.17841391852538</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.7356009037443092</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2933615252620193</v>
+      </c>
+      <c r="C94">
+        <v>-25.94157098179588</v>
+      </c>
+      <c r="D94">
+        <v>46.82242901820413</v>
+      </c>
+      <c r="E94">
+        <v>69.004</v>
+      </c>
+      <c r="F94">
+        <v>75.854</v>
+      </c>
+      <c r="G94">
+        <v>3.09</v>
+      </c>
+      <c r="H94">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>11.9</v>
+      </c>
+      <c r="K94">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L94">
+        <v>11.8</v>
+      </c>
+      <c r="M94">
+        <v>16.2175852</v>
+      </c>
+      <c r="N94">
+        <v>-4.417585199999998</v>
+      </c>
+      <c r="O94">
+        <v>-0.9939566699999994</v>
+      </c>
+      <c r="P94">
+        <v>-3.423628529999998</v>
+      </c>
+      <c r="Q94">
+        <v>-3.323628529999999</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>1.610835742549044</v>
+      </c>
+      <c r="T94">
+        <v>10.2027224021336</v>
+      </c>
+      <c r="U94">
+        <v>0.2138</v>
+      </c>
+      <c r="V94">
+        <v>0.1637111793930948</v>
+      </c>
+      <c r="W94">
+        <v>0.1787985498457563</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.7276052417470884</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2951115252620192</v>
+      </c>
+      <c r="C95">
+        <v>-27.08575715547883</v>
+      </c>
+      <c r="D95">
+        <v>46.50274284452117</v>
+      </c>
+      <c r="E95">
+        <v>69.82850000000001</v>
+      </c>
+      <c r="F95">
+        <v>76.6785</v>
+      </c>
+      <c r="G95">
+        <v>3.09</v>
+      </c>
+      <c r="H95">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>11.9</v>
+      </c>
+      <c r="K95">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L95">
+        <v>11.8</v>
+      </c>
+      <c r="M95">
+        <v>16.3938633</v>
+      </c>
+      <c r="N95">
+        <v>-4.593863299999999</v>
+      </c>
+      <c r="O95">
+        <v>-1.0336192425</v>
+      </c>
+      <c r="P95">
+        <v>-3.560244057499999</v>
+      </c>
+      <c r="Q95">
+        <v>-3.4602440575</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.835412277198907</v>
+      </c>
+      <c r="T95">
+        <v>11.66025417386697</v>
+      </c>
+      <c r="U95">
+        <v>0.2138</v>
+      </c>
+      <c r="V95">
+        <v>0.1619508441308035</v>
+      </c>
+      <c r="W95">
+        <v>0.1791749095248342</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.7197815294702379</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2968615252620193</v>
+      </c>
+      <c r="C96">
+        <v>-28.22560753518106</v>
+      </c>
+      <c r="D96">
+        <v>46.18739246481895</v>
+      </c>
+      <c r="E96">
+        <v>70.65300000000001</v>
+      </c>
+      <c r="F96">
+        <v>77.503</v>
+      </c>
+      <c r="G96">
+        <v>3.09</v>
+      </c>
+      <c r="H96">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>11.9</v>
+      </c>
+      <c r="K96">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L96">
+        <v>11.8</v>
+      </c>
+      <c r="M96">
+        <v>16.5701414</v>
+      </c>
+      <c r="N96">
+        <v>-4.7701414</v>
+      </c>
+      <c r="O96">
+        <v>-1.073281815</v>
+      </c>
+      <c r="P96">
+        <v>-3.696859585</v>
+      </c>
+      <c r="Q96">
+        <v>-3.596859585000001</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>2.13484765673206</v>
+      </c>
+      <c r="T96">
+        <v>13.60362986951147</v>
+      </c>
+      <c r="U96">
+        <v>0.2138</v>
+      </c>
+      <c r="V96">
+        <v>0.160227962810263</v>
+      </c>
+      <c r="W96">
+        <v>0.1795432615511658</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.7121242791567246</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2986115252620193</v>
+      </c>
+      <c r="C97">
+        <v>-29.36120973409975</v>
+      </c>
+      <c r="D97">
+        <v>45.87629026590025</v>
+      </c>
+      <c r="E97">
+        <v>71.47750000000001</v>
+      </c>
+      <c r="F97">
+        <v>78.3275</v>
+      </c>
+      <c r="G97">
+        <v>3.09</v>
+      </c>
+      <c r="H97">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>11.9</v>
+      </c>
+      <c r="K97">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L97">
+        <v>11.8</v>
+      </c>
+      <c r="M97">
+        <v>16.7464195</v>
+      </c>
+      <c r="N97">
+        <v>-4.946419499999998</v>
+      </c>
+      <c r="O97">
+        <v>-1.112944387499999</v>
+      </c>
+      <c r="P97">
+        <v>-3.833475112499998</v>
+      </c>
+      <c r="Q97">
+        <v>-3.733475112499999</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>2.554057188078473</v>
+      </c>
+      <c r="T97">
+        <v>16.32435584341377</v>
+      </c>
+      <c r="U97">
+        <v>0.2138</v>
+      </c>
+      <c r="V97">
+        <v>0.1585413526754182</v>
+      </c>
+      <c r="W97">
+        <v>0.1799038587979956</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.7046282341129697</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.3003615252620193</v>
+      </c>
+      <c r="C98">
+        <v>-30.49264902069741</v>
+      </c>
+      <c r="D98">
+        <v>45.56935097930258</v>
+      </c>
+      <c r="E98">
+        <v>72.30199999999999</v>
+      </c>
+      <c r="F98">
+        <v>79.15199999999999</v>
+      </c>
+      <c r="G98">
+        <v>3.09</v>
+      </c>
+      <c r="H98">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>11.9</v>
+      </c>
+      <c r="K98">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L98">
+        <v>11.8</v>
+      </c>
+      <c r="M98">
+        <v>16.9226976</v>
+      </c>
+      <c r="N98">
+        <v>-5.122697599999995</v>
+      </c>
+      <c r="O98">
+        <v>-1.152606959999999</v>
+      </c>
+      <c r="P98">
+        <v>-3.970090639999996</v>
+      </c>
+      <c r="Q98">
+        <v>-3.870090639999996</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>3.182871485098083</v>
+      </c>
+      <c r="T98">
+        <v>20.40544480426717</v>
+      </c>
+      <c r="U98">
+        <v>0.2138</v>
+      </c>
+      <c r="V98">
+        <v>0.1568898802517159</v>
+      </c>
+      <c r="W98">
+        <v>0.1802569436021831</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.6972883566742931</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.3021115252620193</v>
+      </c>
+      <c r="C99">
+        <v>-31.62000839661886</v>
+      </c>
+      <c r="D99">
+        <v>45.26649160338113</v>
+      </c>
+      <c r="E99">
+        <v>73.12649999999999</v>
+      </c>
+      <c r="F99">
+        <v>79.97649999999999</v>
+      </c>
+      <c r="G99">
+        <v>3.09</v>
+      </c>
+      <c r="H99">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>11.9</v>
+      </c>
+      <c r="K99">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L99">
+        <v>11.8</v>
+      </c>
+      <c r="M99">
+        <v>17.0989757</v>
+      </c>
+      <c r="N99">
+        <v>-5.298975699999996</v>
+      </c>
+      <c r="O99">
+        <v>-1.192269532499999</v>
+      </c>
+      <c r="P99">
+        <v>-4.106706167499997</v>
+      </c>
+      <c r="Q99">
+        <v>-4.006706167499997</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>4.230895313464112</v>
+      </c>
+      <c r="T99">
+        <v>27.20725973902289</v>
+      </c>
+      <c r="U99">
+        <v>0.2138</v>
+      </c>
+      <c r="V99">
+        <v>0.1552724588058219</v>
+      </c>
+      <c r="W99">
+        <v>0.1806027483073153</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.6900998169147643</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.3038615252620192</v>
+      </c>
+      <c r="C100">
+        <v>-32.74336867152147</v>
+      </c>
+      <c r="D100">
+        <v>44.96763132847852</v>
+      </c>
+      <c r="E100">
+        <v>73.95099999999999</v>
+      </c>
+      <c r="F100">
+        <v>80.80099999999999</v>
+      </c>
+      <c r="G100">
+        <v>3.09</v>
+      </c>
+      <c r="H100">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>11.9</v>
+      </c>
+      <c r="K100">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L100">
+        <v>11.8</v>
+      </c>
+      <c r="M100">
+        <v>17.2752538</v>
+      </c>
+      <c r="N100">
+        <v>-5.475253799999997</v>
+      </c>
+      <c r="O100">
+        <v>-1.231932104999999</v>
+      </c>
+      <c r="P100">
+        <v>-4.243321694999998</v>
+      </c>
+      <c r="Q100">
+        <v>-4.143321694999998</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>6.326942970196166</v>
+      </c>
+      <c r="T100">
+        <v>40.81088960853432</v>
+      </c>
+      <c r="U100">
+        <v>0.2138</v>
+      </c>
+      <c r="V100">
+        <v>0.1536880459608646</v>
+      </c>
+      <c r="W100">
+        <v>0.1809414957735671</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.6830579820482869</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.3056115252620192</v>
+      </c>
+      <c r="C101">
+        <v>-33.86280853496088</v>
+      </c>
+      <c r="D101">
+        <v>44.67269146503912</v>
+      </c>
+      <c r="E101">
+        <v>74.77549999999999</v>
+      </c>
+      <c r="F101">
+        <v>81.62549999999999</v>
+      </c>
+      <c r="G101">
+        <v>3.09</v>
+      </c>
+      <c r="H101">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>11.9</v>
+      </c>
+      <c r="K101">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="L101">
+        <v>11.8</v>
+      </c>
+      <c r="M101">
+        <v>17.4515319</v>
+      </c>
+      <c r="N101">
+        <v>-5.651531899999995</v>
+      </c>
+      <c r="O101">
+        <v>-1.271594677499999</v>
+      </c>
+      <c r="P101">
+        <v>-4.379937222499996</v>
+      </c>
+      <c r="Q101">
+        <v>-4.279937222499997</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>12.61508594039233</v>
+      </c>
+      <c r="T101">
+        <v>81.62177921706865</v>
+      </c>
+      <c r="U101">
+        <v>0.2138</v>
+      </c>
+      <c r="V101">
+        <v>0.1521356414562094</v>
+      </c>
+      <c r="W101">
+        <v>0.1812733998566624</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.6761584064720418</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
